--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -901,7 +901,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>4379</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>7125</v>
       </c>
       <c r="M3">
-        <v>4925</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>1953</v>
       </c>
       <c r="M4">
-        <v>1308</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>434</v>
       </c>
       <c r="M5">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>5817</v>
       </c>
       <c r="M6">
-        <v>3225</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>21917</v>
       </c>
       <c r="M7">
-        <v>14133</v>
+        <v>14230</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2086,7 @@
         <v>78</v>
       </c>
       <c r="M2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2127,7 +2127,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2250,7 +2250,7 @@
         <v>67</v>
       </c>
       <c r="M6">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2291,7 +2291,7 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2398,7 +2398,7 @@
         <v>370</v>
       </c>
       <c r="M2">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2439,7 +2439,7 @@
         <v>465</v>
       </c>
       <c r="M3">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2480,7 +2480,7 @@
         <v>66</v>
       </c>
       <c r="M4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2562,7 +2562,7 @@
         <v>287</v>
       </c>
       <c r="M6">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2603,7 +2603,7 @@
         <v>1209</v>
       </c>
       <c r="M7">
-        <v>788</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2710,7 @@
         <v>187</v>
       </c>
       <c r="M2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2915,7 +2915,7 @@
         <v>602</v>
       </c>
       <c r="M7">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -3063,7 +3063,7 @@
         <v>294</v>
       </c>
       <c r="M3">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3186,7 +3186,7 @@
         <v>210</v>
       </c>
       <c r="M6">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3227,7 +3227,7 @@
         <v>830</v>
       </c>
       <c r="M7">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -3375,7 +3375,7 @@
         <v>131</v>
       </c>
       <c r="M3">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3498,7 +3498,7 @@
         <v>39</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3539,7 +3539,7 @@
         <v>296</v>
       </c>
       <c r="M7">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3969,7 +3969,7 @@
         <v>235</v>
       </c>
       <c r="M3">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4092,7 +4092,7 @@
         <v>190</v>
       </c>
       <c r="M6">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4133,7 +4133,7 @@
         <v>683</v>
       </c>
       <c r="M7">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -4751,7 +4751,7 @@
         <v>693</v>
       </c>
       <c r="M7">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4792,7 +4792,7 @@
         <v>1430</v>
       </c>
       <c r="M8">
-        <v>967</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4915,7 +4915,7 @@
         <v>352</v>
       </c>
       <c r="M11">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4956,7 +4956,7 @@
         <v>51</v>
       </c>
       <c r="M12">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -5079,7 +5079,7 @@
         <v>189</v>
       </c>
       <c r="M15">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -5243,7 +5243,7 @@
         <v>595</v>
       </c>
       <c r="M19">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5284,7 +5284,7 @@
         <v>540</v>
       </c>
       <c r="M20">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5489,7 +5489,7 @@
         <v>128</v>
       </c>
       <c r="M25">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5571,7 +5571,7 @@
         <v>192</v>
       </c>
       <c r="M27">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5653,7 +5653,7 @@
         <v>1209</v>
       </c>
       <c r="M29">
-        <v>788</v>
+        <v>793</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5817,7 +5817,7 @@
         <v>975</v>
       </c>
       <c r="M33">
-        <v>603</v>
+        <v>611</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5940,7 +5940,7 @@
         <v>272</v>
       </c>
       <c r="M36">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5981,7 +5981,7 @@
         <v>830</v>
       </c>
       <c r="M37">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6063,7 +6063,7 @@
         <v>13</v>
       </c>
       <c r="M39">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -6145,7 +6145,7 @@
         <v>92</v>
       </c>
       <c r="M41">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -6186,7 +6186,7 @@
         <v>683</v>
       </c>
       <c r="M42">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6227,7 +6227,7 @@
         <v>166</v>
       </c>
       <c r="M43">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -6432,7 +6432,7 @@
         <v>277</v>
       </c>
       <c r="M48">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6555,7 +6555,7 @@
         <v>267</v>
       </c>
       <c r="M51">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6637,7 +6637,7 @@
         <v>236</v>
       </c>
       <c r="M53">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6678,7 +6678,7 @@
         <v>452</v>
       </c>
       <c r="M54">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6719,7 +6719,7 @@
         <v>227</v>
       </c>
       <c r="M55">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6801,7 +6801,7 @@
         <v>75</v>
       </c>
       <c r="M57">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -6924,7 +6924,7 @@
         <v>144</v>
       </c>
       <c r="M60">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -7047,7 +7047,7 @@
         <v>328</v>
       </c>
       <c r="M63">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7129,7 +7129,7 @@
         <v>435</v>
       </c>
       <c r="M65">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7211,7 +7211,7 @@
         <v>756</v>
       </c>
       <c r="M67">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7580,7 +7580,7 @@
         <v>350</v>
       </c>
       <c r="M76">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7703,7 +7703,7 @@
         <v>602</v>
       </c>
       <c r="M79">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7867,7 +7867,7 @@
         <v>480</v>
       </c>
       <c r="M83">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7908,7 +7908,7 @@
         <v>208</v>
       </c>
       <c r="M84">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7949,7 +7949,7 @@
         <v>1080</v>
       </c>
       <c r="M85">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -8072,7 +8072,7 @@
         <v>224</v>
       </c>
       <c r="M88">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -8195,7 +8195,7 @@
         <v>296</v>
       </c>
       <c r="M91">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -8277,7 +8277,7 @@
         <v>109</v>
       </c>
       <c r="M93">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -8318,7 +8318,7 @@
         <v>260</v>
       </c>
       <c r="M94">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -8359,7 +8359,7 @@
         <v>302</v>
       </c>
       <c r="M95">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8400,7 +8400,7 @@
         <v>240</v>
       </c>
       <c r="M96">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -8605,7 +8605,7 @@
         <v>21917</v>
       </c>
       <c r="M101">
-        <v>14133</v>
+        <v>14230</v>
       </c>
     </row>
   </sheetData>
@@ -8855,7 +8855,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9019,7 +9019,7 @@
         <v>227</v>
       </c>
       <c r="M7">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -9167,7 +9167,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9331,7 +9331,7 @@
         <v>756</v>
       </c>
       <c r="M7">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -9479,7 +9479,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9520,7 +9520,7 @@
         <v>48</v>
       </c>
       <c r="M4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9643,7 +9643,7 @@
         <v>540</v>
       </c>
       <c r="M7">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -9914,7 +9914,7 @@
         <v>107</v>
       </c>
       <c r="M6">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9955,7 +9955,7 @@
         <v>480</v>
       </c>
       <c r="M7">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -10062,7 +10062,7 @@
         <v>133</v>
       </c>
       <c r="M2">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10103,7 +10103,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10223,7 +10223,7 @@
         <v>90</v>
       </c>
       <c r="M6">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10264,7 +10264,7 @@
         <v>352</v>
       </c>
       <c r="M7">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -10724,7 +10724,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10888,7 +10888,7 @@
         <v>435</v>
       </c>
       <c r="M7">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -12503,7 +12503,7 @@
         <v>67</v>
       </c>
       <c r="M3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12544,7 +12544,7 @@
         <v>44</v>
       </c>
       <c r="M4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -12626,7 +12626,7 @@
         <v>161</v>
       </c>
       <c r="M6">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12667,7 +12667,7 @@
         <v>350</v>
       </c>
       <c r="M7">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -12774,7 +12774,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12929,7 +12929,7 @@
         <v>13</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -13345,7 +13345,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13467,6 +13467,9 @@
       <c r="L5">
         <v>1</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -13547,7 +13550,7 @@
         <v>236</v>
       </c>
       <c r="M7">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -13966,7 +13969,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14007,7 +14010,7 @@
         <v>504</v>
       </c>
       <c r="M3">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14089,7 +14092,7 @@
         <v>44</v>
       </c>
       <c r="M5">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -14130,7 +14133,7 @@
         <v>342</v>
       </c>
       <c r="M6">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14171,7 +14174,7 @@
         <v>1430</v>
       </c>
       <c r="M7">
-        <v>967</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -14319,7 +14322,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14471,7 +14474,7 @@
         <v>166</v>
       </c>
       <c r="M7">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -14913,7 +14916,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15036,7 +15039,7 @@
         <v>38</v>
       </c>
       <c r="M6">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15077,7 +15080,7 @@
         <v>189</v>
       </c>
       <c r="M7">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -15225,7 +15228,7 @@
         <v>69</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15377,7 +15380,7 @@
         <v>277</v>
       </c>
       <c r="M7">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -15484,7 +15487,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15525,7 +15528,7 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15566,7 +15569,7 @@
         <v>20</v>
       </c>
       <c r="M4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15689,7 +15692,7 @@
         <v>302</v>
       </c>
       <c r="M7">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -16475,7 +16478,7 @@
         <v>43</v>
       </c>
       <c r="M4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -16598,7 +16601,7 @@
         <v>693</v>
       </c>
       <c r="M7">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -16746,7 +16749,7 @@
         <v>180</v>
       </c>
       <c r="M3">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16869,7 +16872,7 @@
         <v>165</v>
       </c>
       <c r="M6">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16910,7 +16913,7 @@
         <v>595</v>
       </c>
       <c r="M7">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -17175,7 +17178,7 @@
         <v>94</v>
       </c>
       <c r="M6">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17216,7 +17219,7 @@
         <v>260</v>
       </c>
       <c r="M7">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -18547,7 +18550,7 @@
         <v>266</v>
       </c>
       <c r="M2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18588,7 +18591,7 @@
         <v>342</v>
       </c>
       <c r="M3">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18629,7 +18632,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18711,7 +18714,7 @@
         <v>271</v>
       </c>
       <c r="M6">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18752,7 +18755,7 @@
         <v>975</v>
       </c>
       <c r="M7">
-        <v>603</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -19153,7 +19156,7 @@
         <v>38</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19349,7 +19352,7 @@
         <v>109</v>
       </c>
       <c r="M7">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -19497,7 +19500,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19661,7 +19664,7 @@
         <v>208</v>
       </c>
       <c r="M7">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -20756,7 +20759,7 @@
         <v>41</v>
       </c>
       <c r="M4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -20838,7 +20841,7 @@
         <v>57</v>
       </c>
       <c r="M6">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -20879,7 +20882,7 @@
         <v>267</v>
       </c>
       <c r="M7">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -21250,7 +21253,7 @@
         <v>85</v>
       </c>
       <c r="M2">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21411,7 +21414,7 @@
         <v>207</v>
       </c>
       <c r="M6">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21452,7 +21455,7 @@
         <v>452</v>
       </c>
       <c r="M7">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -21559,7 +21562,7 @@
         <v>42</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21764,7 +21767,7 @@
         <v>128</v>
       </c>
       <c r="M7">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -21994,7 +21997,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -22076,7 +22079,7 @@
         <v>224</v>
       </c>
       <c r="M7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -23253,7 +23256,7 @@
         <v>38</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23294,7 +23297,7 @@
         <v>144</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -24019,7 +24022,7 @@
         <v>25</v>
       </c>
       <c r="M2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24218,7 +24221,7 @@
         <v>75</v>
       </c>
       <c r="M7">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -25275,7 +25278,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25316,7 +25319,7 @@
         <v>22</v>
       </c>
       <c r="M4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -25436,7 +25439,7 @@
         <v>272</v>
       </c>
       <c r="M7">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -25584,7 +25587,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25724,7 +25727,7 @@
         <v>51</v>
       </c>
       <c r="M7">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -26122,7 +26125,7 @@
         <v>51</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26321,7 +26324,7 @@
         <v>192</v>
       </c>
       <c r="M7">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -27358,7 +27361,7 @@
         <v>29</v>
       </c>
       <c r="M2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -27440,7 +27443,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -27551,7 +27554,7 @@
         <v>92</v>
       </c>
       <c r="M7">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -28546,7 +28549,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28587,7 +28590,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28751,7 +28754,7 @@
         <v>1080</v>
       </c>
       <c r="M7">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -50,8 +50,8 @@
     <sheet name="Morgan Park" sheetId="41" r:id="rId41"/>
     <sheet name="Near South Side" sheetId="42" r:id="rId42"/>
     <sheet name="Mckinley Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Garfield Park" sheetId="44" r:id="rId44"/>
-    <sheet name="Rogers Park" sheetId="45" r:id="rId45"/>
+    <sheet name="Rogers Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Garfield Park" sheetId="45" r:id="rId45"/>
     <sheet name="Brighton Park" sheetId="46" r:id="rId46"/>
     <sheet name="West Elsdon" sheetId="47" r:id="rId47"/>
     <sheet name="Hyde Park" sheetId="48" r:id="rId48"/>
@@ -16815,40 +16815,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>210</v>
+        <v>51</v>
       </c>
       <c r="C2">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="D2">
-        <v>276</v>
+        <v>52</v>
       </c>
       <c r="E2">
-        <v>265</v>
+        <v>56</v>
       </c>
       <c r="F2">
-        <v>238</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>249</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>284</v>
+        <v>69</v>
       </c>
       <c r="I2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="J2">
-        <v>293</v>
+        <v>88</v>
       </c>
       <c r="K2">
-        <v>285</v>
+        <v>102</v>
       </c>
       <c r="L2">
-        <v>265</v>
+        <v>75</v>
       </c>
       <c r="M2">
-        <v>178</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16856,40 +16856,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>387</v>
+        <v>74</v>
       </c>
       <c r="C3">
-        <v>491</v>
+        <v>77</v>
       </c>
       <c r="D3">
-        <v>480</v>
+        <v>62</v>
       </c>
       <c r="E3">
-        <v>522</v>
+        <v>56</v>
       </c>
       <c r="F3">
-        <v>520</v>
+        <v>62</v>
       </c>
       <c r="G3">
-        <v>574</v>
+        <v>69</v>
       </c>
       <c r="H3">
-        <v>531</v>
+        <v>93</v>
       </c>
       <c r="I3">
-        <v>417</v>
+        <v>88</v>
       </c>
       <c r="J3">
-        <v>435</v>
+        <v>104</v>
       </c>
       <c r="K3">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="L3">
-        <v>341</v>
+        <v>93</v>
       </c>
       <c r="M3">
-        <v>261</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16897,37 +16897,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C4">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H4">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="I4">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="J4">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K4">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="L4">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="M4">
         <v>32</v>
@@ -16938,40 +16938,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16979,40 +16979,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>527</v>
+        <v>103</v>
       </c>
       <c r="C6">
-        <v>579</v>
+        <v>157</v>
       </c>
       <c r="D6">
-        <v>553</v>
+        <v>163</v>
       </c>
       <c r="E6">
-        <v>608</v>
+        <v>139</v>
       </c>
       <c r="F6">
-        <v>458</v>
+        <v>109</v>
       </c>
       <c r="G6">
-        <v>491</v>
+        <v>115</v>
       </c>
       <c r="H6">
-        <v>357</v>
+        <v>165</v>
       </c>
       <c r="I6">
-        <v>364</v>
+        <v>129</v>
       </c>
       <c r="J6">
-        <v>473</v>
+        <v>105</v>
       </c>
       <c r="K6">
-        <v>363</v>
+        <v>108</v>
       </c>
       <c r="L6">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="M6">
-        <v>156</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17020,40 +17020,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1214</v>
+        <v>260</v>
       </c>
       <c r="C7">
-        <v>1448</v>
+        <v>332</v>
       </c>
       <c r="D7">
-        <v>1401</v>
+        <v>318</v>
       </c>
       <c r="E7">
-        <v>1510</v>
+        <v>280</v>
       </c>
       <c r="F7">
-        <v>1318</v>
+        <v>284</v>
       </c>
       <c r="G7">
-        <v>1429</v>
+        <v>306</v>
       </c>
       <c r="H7">
-        <v>1302</v>
+        <v>355</v>
       </c>
       <c r="I7">
-        <v>1147</v>
+        <v>345</v>
       </c>
       <c r="J7">
-        <v>1312</v>
+        <v>339</v>
       </c>
       <c r="K7">
-        <v>1145</v>
+        <v>334</v>
       </c>
       <c r="L7">
-        <v>973</v>
+        <v>287</v>
       </c>
       <c r="M7">
-        <v>658</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -17127,40 +17127,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C2">
-        <v>63</v>
+        <v>250</v>
       </c>
       <c r="D2">
-        <v>52</v>
+        <v>276</v>
       </c>
       <c r="E2">
-        <v>56</v>
+        <v>265</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>238</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>249</v>
       </c>
       <c r="H2">
-        <v>69</v>
+        <v>284</v>
       </c>
       <c r="I2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="J2">
-        <v>88</v>
+        <v>293</v>
       </c>
       <c r="K2">
-        <v>102</v>
+        <v>285</v>
       </c>
       <c r="L2">
-        <v>75</v>
+        <v>265</v>
       </c>
       <c r="M2">
-        <v>52</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17168,40 +17168,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>74</v>
+        <v>387</v>
       </c>
       <c r="C3">
-        <v>77</v>
+        <v>491</v>
       </c>
       <c r="D3">
-        <v>62</v>
+        <v>480</v>
       </c>
       <c r="E3">
-        <v>56</v>
+        <v>522</v>
       </c>
       <c r="F3">
-        <v>62</v>
+        <v>520</v>
       </c>
       <c r="G3">
-        <v>69</v>
+        <v>574</v>
       </c>
       <c r="H3">
-        <v>93</v>
+        <v>531</v>
       </c>
       <c r="I3">
-        <v>88</v>
+        <v>417</v>
       </c>
       <c r="J3">
-        <v>104</v>
+        <v>435</v>
       </c>
       <c r="K3">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="L3">
-        <v>93</v>
+        <v>341</v>
       </c>
       <c r="M3">
-        <v>69</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17209,37 +17209,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="G4">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H4">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="I4">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K4">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="L4">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="M4">
         <v>32</v>
@@ -17250,40 +17250,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17291,40 +17291,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>103</v>
+        <v>527</v>
       </c>
       <c r="C6">
-        <v>157</v>
+        <v>579</v>
       </c>
       <c r="D6">
-        <v>163</v>
+        <v>553</v>
       </c>
       <c r="E6">
-        <v>139</v>
+        <v>608</v>
       </c>
       <c r="F6">
-        <v>109</v>
+        <v>458</v>
       </c>
       <c r="G6">
-        <v>115</v>
+        <v>491</v>
       </c>
       <c r="H6">
-        <v>165</v>
+        <v>357</v>
       </c>
       <c r="I6">
-        <v>129</v>
+        <v>364</v>
       </c>
       <c r="J6">
-        <v>105</v>
+        <v>473</v>
       </c>
       <c r="K6">
-        <v>108</v>
+        <v>363</v>
       </c>
       <c r="L6">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="M6">
-        <v>44</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17332,40 +17332,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>260</v>
+        <v>1214</v>
       </c>
       <c r="C7">
-        <v>332</v>
+        <v>1448</v>
       </c>
       <c r="D7">
-        <v>318</v>
+        <v>1401</v>
       </c>
       <c r="E7">
-        <v>280</v>
+        <v>1510</v>
       </c>
       <c r="F7">
-        <v>284</v>
+        <v>1318</v>
       </c>
       <c r="G7">
-        <v>306</v>
+        <v>1429</v>
       </c>
       <c r="H7">
-        <v>355</v>
+        <v>1302</v>
       </c>
       <c r="I7">
-        <v>345</v>
+        <v>1147</v>
       </c>
       <c r="J7">
-        <v>339</v>
+        <v>1312</v>
       </c>
       <c r="K7">
-        <v>334</v>
+        <v>1145</v>
       </c>
       <c r="L7">
-        <v>287</v>
+        <v>973</v>
       </c>
       <c r="M7">
-        <v>199</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -901,7 +901,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>4878</v>
+        <v>4895</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>7126</v>
       </c>
       <c r="M3">
-        <v>5484</v>
+        <v>5506</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>1956</v>
       </c>
       <c r="M4">
-        <v>1486</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>435</v>
       </c>
       <c r="M5">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>5816</v>
       </c>
       <c r="M6">
-        <v>3596</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>21921</v>
       </c>
       <c r="M7">
-        <v>15773</v>
+        <v>15839</v>
       </c>
     </row>
   </sheetData>
@@ -1377,7 +1377,7 @@
         <v>82</v>
       </c>
       <c r="M6">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1418,7 +1418,7 @@
         <v>287</v>
       </c>
       <c r="M7">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2092,7 @@
         <v>78</v>
       </c>
       <c r="M2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2133,7 +2133,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2297,7 +2297,7 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2568,7 +2568,7 @@
         <v>286</v>
       </c>
       <c r="M6">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2609,7 +2609,7 @@
         <v>1206</v>
       </c>
       <c r="M7">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
   </sheetData>
@@ -2716,7 +2716,7 @@
         <v>185</v>
       </c>
       <c r="M2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2757,7 +2757,7 @@
         <v>195</v>
       </c>
       <c r="M3">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2880,7 +2880,7 @@
         <v>161</v>
       </c>
       <c r="M6">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2921,7 +2921,7 @@
         <v>598</v>
       </c>
       <c r="M7">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -3028,7 +3028,7 @@
         <v>249</v>
       </c>
       <c r="M2">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3110,7 +3110,7 @@
         <v>52</v>
       </c>
       <c r="M4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3192,7 +3192,7 @@
         <v>209</v>
       </c>
       <c r="M6">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3233,7 +3233,7 @@
         <v>827</v>
       </c>
       <c r="M7">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -3975,7 +3975,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4098,7 +4098,7 @@
         <v>190</v>
       </c>
       <c r="M6">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4139,7 +4139,7 @@
         <v>682</v>
       </c>
       <c r="M7">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -4246,7 +4246,7 @@
         <v>34</v>
       </c>
       <c r="M2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4445,7 +4445,7 @@
         <v>106</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4552,7 +4552,7 @@
         <v>190</v>
       </c>
       <c r="M2">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4634,7 +4634,7 @@
         <v>78</v>
       </c>
       <c r="M4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4757,7 +4757,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4798,7 +4798,7 @@
         <v>1427</v>
       </c>
       <c r="M8">
-        <v>1082</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4921,7 +4921,7 @@
         <v>351</v>
       </c>
       <c r="M11">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5085,7 +5085,7 @@
         <v>187</v>
       </c>
       <c r="M15">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -5208,7 +5208,7 @@
         <v>149</v>
       </c>
       <c r="M18">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -5249,7 +5249,7 @@
         <v>593</v>
       </c>
       <c r="M19">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5413,7 +5413,7 @@
         <v>231</v>
       </c>
       <c r="M23">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5659,7 +5659,7 @@
         <v>1206</v>
       </c>
       <c r="M29">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5741,7 +5741,7 @@
         <v>213</v>
       </c>
       <c r="M31">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5823,7 +5823,7 @@
         <v>973</v>
       </c>
       <c r="M33">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5864,7 +5864,7 @@
         <v>118</v>
       </c>
       <c r="M34">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -5987,7 +5987,7 @@
         <v>827</v>
       </c>
       <c r="M37">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6192,7 +6192,7 @@
         <v>682</v>
       </c>
       <c r="M42">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6233,7 +6233,7 @@
         <v>167</v>
       </c>
       <c r="M43">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -6274,7 +6274,7 @@
         <v>148</v>
       </c>
       <c r="M44">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -6479,7 +6479,7 @@
         <v>112</v>
       </c>
       <c r="M49">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6520,7 +6520,7 @@
         <v>106</v>
       </c>
       <c r="M50">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6602,7 +6602,7 @@
         <v>459</v>
       </c>
       <c r="M52">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6643,7 +6643,7 @@
         <v>233</v>
       </c>
       <c r="M53">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -7053,7 +7053,7 @@
         <v>386</v>
       </c>
       <c r="M63">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7094,7 +7094,7 @@
         <v>138</v>
       </c>
       <c r="M64">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -7135,7 +7135,7 @@
         <v>434</v>
       </c>
       <c r="M65">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7217,7 +7217,7 @@
         <v>753</v>
       </c>
       <c r="M67">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7340,7 +7340,7 @@
         <v>36</v>
       </c>
       <c r="M70">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -7463,7 +7463,7 @@
         <v>171</v>
       </c>
       <c r="M73">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7545,7 +7545,7 @@
         <v>79</v>
       </c>
       <c r="M75">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -7668,7 +7668,7 @@
         <v>287</v>
       </c>
       <c r="M78">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7709,7 +7709,7 @@
         <v>598</v>
       </c>
       <c r="M79">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7914,7 +7914,7 @@
         <v>208</v>
       </c>
       <c r="M84">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7955,7 +7955,7 @@
         <v>1080</v>
       </c>
       <c r="M85">
-        <v>808</v>
+        <v>813</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -8160,7 +8160,7 @@
         <v>230</v>
       </c>
       <c r="M90">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -8283,7 +8283,7 @@
         <v>109</v>
       </c>
       <c r="M93">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -8365,7 +8365,7 @@
         <v>302</v>
       </c>
       <c r="M95">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8406,7 +8406,7 @@
         <v>240</v>
       </c>
       <c r="M96">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -8529,7 +8529,7 @@
         <v>373</v>
       </c>
       <c r="M99">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8611,7 +8611,7 @@
         <v>21921</v>
       </c>
       <c r="M101">
-        <v>15773</v>
+        <v>15839</v>
       </c>
     </row>
   </sheetData>
@@ -9173,7 +9173,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9296,7 +9296,7 @@
         <v>175</v>
       </c>
       <c r="M6">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9337,7 +9337,7 @@
         <v>753</v>
       </c>
       <c r="M7">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -10068,7 +10068,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10190,6 +10190,9 @@
       <c r="L5">
         <v>4</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -10270,7 +10273,7 @@
         <v>351</v>
       </c>
       <c r="M7">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -10730,7 +10733,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10853,7 +10856,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10894,7 +10897,7 @@
         <v>434</v>
       </c>
       <c r="M7">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -11939,7 +11942,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12091,7 +12094,7 @@
         <v>78</v>
       </c>
       <c r="M7">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -13518,7 +13521,7 @@
         <v>77</v>
       </c>
       <c r="M6">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13559,7 +13562,7 @@
         <v>233</v>
       </c>
       <c r="M7">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -13707,7 +13710,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13871,7 +13874,7 @@
         <v>230</v>
       </c>
       <c r="M7">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -13978,7 +13981,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14019,7 +14022,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14060,7 +14063,7 @@
         <v>104</v>
       </c>
       <c r="M4">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14142,7 +14145,7 @@
         <v>340</v>
       </c>
       <c r="M6">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14183,7 +14186,7 @@
         <v>1427</v>
       </c>
       <c r="M7">
-        <v>1082</v>
+        <v>1094</v>
       </c>
     </row>
   </sheetData>
@@ -14331,7 +14334,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14483,7 +14486,7 @@
         <v>167</v>
       </c>
       <c r="M7">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -15048,7 +15051,7 @@
         <v>37</v>
       </c>
       <c r="M6">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15089,7 +15092,7 @@
         <v>187</v>
       </c>
       <c r="M7">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -15496,7 +15499,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15701,7 +15704,7 @@
         <v>302</v>
       </c>
       <c r="M7">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -16446,7 +16449,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16610,7 +16613,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -17461,7 +17464,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17502,7 +17505,7 @@
         <v>164</v>
       </c>
       <c r="M6">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17543,7 +17546,7 @@
         <v>593</v>
       </c>
       <c r="M7">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -17650,7 +17653,7 @@
         <v>113</v>
       </c>
       <c r="M2">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17691,7 +17694,7 @@
         <v>150</v>
       </c>
       <c r="M3">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17814,7 +17817,7 @@
         <v>79</v>
       </c>
       <c r="M6">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17855,7 +17858,7 @@
         <v>373</v>
       </c>
       <c r="M7">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -18274,7 +18277,7 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18464,7 +18467,7 @@
         <v>112</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -18571,7 +18574,7 @@
         <v>265</v>
       </c>
       <c r="M2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18612,7 +18615,7 @@
         <v>341</v>
       </c>
       <c r="M3">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18735,7 +18738,7 @@
         <v>271</v>
       </c>
       <c r="M6">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18776,7 +18779,7 @@
         <v>973</v>
       </c>
       <c r="M7">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -20153,7 +20156,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -20249,7 +20252,7 @@
         <v>36</v>
       </c>
       <c r="M7">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -21294,7 +21297,7 @@
         <v>51</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21458,7 +21461,7 @@
         <v>149</v>
       </c>
       <c r="M7">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -22635,7 +22638,7 @@
         <v>40</v>
       </c>
       <c r="M6">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22676,7 +22679,7 @@
         <v>171</v>
       </c>
       <c r="M7">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -22783,7 +22786,7 @@
         <v>84</v>
       </c>
       <c r="M2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22865,7 +22868,7 @@
         <v>12</v>
       </c>
       <c r="M4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -22988,7 +22991,7 @@
         <v>213</v>
       </c>
       <c r="M7">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -23680,7 +23683,7 @@
         <v>62</v>
       </c>
       <c r="M2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23885,7 +23888,7 @@
         <v>190</v>
       </c>
       <c r="M7">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -24074,7 +24077,7 @@
         <v>16</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24191,7 +24194,7 @@
         <v>138</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -24919,7 +24922,7 @@
         <v>70</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25124,7 +25127,7 @@
         <v>208</v>
       </c>
       <c r="M7">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -27040,7 +27043,7 @@
         <v>38</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -27081,7 +27084,7 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27236,7 +27239,7 @@
         <v>109</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -27919,7 +27922,7 @@
         <v>59</v>
       </c>
       <c r="M2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28124,7 +28127,7 @@
         <v>231</v>
       </c>
       <c r="M7">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -28534,7 +28537,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28575,7 +28578,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28698,7 +28701,7 @@
         <v>226</v>
       </c>
       <c r="M6">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -28739,7 +28742,7 @@
         <v>1080</v>
       </c>
       <c r="M7">
-        <v>808</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -30116,7 +30119,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -30230,7 +30233,7 @@
         <v>79</v>
       </c>
       <c r="M7">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -30768,7 +30771,7 @@
         <v>37</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -30809,7 +30812,7 @@
         <v>148</v>
       </c>
       <c r="M7">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -31821,7 +31824,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -31985,7 +31988,7 @@
         <v>459</v>
       </c>
       <c r="M7">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -33243,7 +33246,7 @@
         <v>32</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -33404,7 +33407,7 @@
         <v>118</v>
       </c>
       <c r="M7">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -901,7 +901,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>4895</v>
+        <v>4911</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>7126</v>
       </c>
       <c r="M3">
-        <v>5506</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>1956</v>
       </c>
       <c r="M4">
-        <v>1492</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>5816</v>
       </c>
       <c r="M6">
-        <v>3615</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>21921</v>
       </c>
       <c r="M7">
-        <v>15839</v>
+        <v>15920</v>
       </c>
     </row>
   </sheetData>
@@ -1377,7 +1377,7 @@
         <v>82</v>
       </c>
       <c r="M6">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1418,7 +1418,7 @@
         <v>287</v>
       </c>
       <c r="M7">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -1830,7 +1830,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1944,7 +1944,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1985,7 +1985,7 @@
         <v>56</v>
       </c>
       <c r="M7">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2404,7 @@
         <v>368</v>
       </c>
       <c r="M2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2445,7 +2445,7 @@
         <v>465</v>
       </c>
       <c r="M3">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2486,7 +2486,7 @@
         <v>66</v>
       </c>
       <c r="M4">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2568,7 +2568,7 @@
         <v>286</v>
       </c>
       <c r="M6">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2609,7 +2609,7 @@
         <v>1206</v>
       </c>
       <c r="M7">
-        <v>862</v>
+        <v>868</v>
       </c>
     </row>
   </sheetData>
@@ -2716,7 +2716,7 @@
         <v>185</v>
       </c>
       <c r="M2">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2757,7 +2757,7 @@
         <v>195</v>
       </c>
       <c r="M3">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2921,7 +2921,7 @@
         <v>598</v>
       </c>
       <c r="M7">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -3028,7 +3028,7 @@
         <v>249</v>
       </c>
       <c r="M2">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3069,7 +3069,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3192,7 +3192,7 @@
         <v>209</v>
       </c>
       <c r="M6">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3233,7 +3233,7 @@
         <v>827</v>
       </c>
       <c r="M7">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -4552,7 +4552,7 @@
         <v>190</v>
       </c>
       <c r="M2">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4757,7 +4757,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4798,7 +4798,7 @@
         <v>1427</v>
       </c>
       <c r="M8">
-        <v>1094</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4880,7 +4880,7 @@
         <v>143</v>
       </c>
       <c r="M10">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4921,7 +4921,7 @@
         <v>351</v>
       </c>
       <c r="M11">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5044,7 +5044,7 @@
         <v>101</v>
       </c>
       <c r="M14">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -5085,7 +5085,7 @@
         <v>187</v>
       </c>
       <c r="M15">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -5249,7 +5249,7 @@
         <v>593</v>
       </c>
       <c r="M19">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5290,7 +5290,7 @@
         <v>539</v>
       </c>
       <c r="M20">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5495,7 +5495,7 @@
         <v>128</v>
       </c>
       <c r="M25">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5577,7 +5577,7 @@
         <v>192</v>
       </c>
       <c r="M27">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5659,7 +5659,7 @@
         <v>1206</v>
       </c>
       <c r="M29">
-        <v>862</v>
+        <v>868</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5741,7 +5741,7 @@
         <v>213</v>
       </c>
       <c r="M31">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5823,7 +5823,7 @@
         <v>973</v>
       </c>
       <c r="M33">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5946,7 +5946,7 @@
         <v>272</v>
       </c>
       <c r="M36">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5987,7 +5987,7 @@
         <v>827</v>
       </c>
       <c r="M37">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6110,7 +6110,7 @@
         <v>57</v>
       </c>
       <c r="M40">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -6233,7 +6233,7 @@
         <v>167</v>
       </c>
       <c r="M43">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -6274,7 +6274,7 @@
         <v>148</v>
       </c>
       <c r="M44">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -6479,7 +6479,7 @@
         <v>112</v>
       </c>
       <c r="M49">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6602,7 +6602,7 @@
         <v>459</v>
       </c>
       <c r="M52">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6684,7 +6684,7 @@
         <v>450</v>
       </c>
       <c r="M54">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6807,7 +6807,7 @@
         <v>75</v>
       </c>
       <c r="M57">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -7053,7 +7053,7 @@
         <v>386</v>
       </c>
       <c r="M63">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7135,7 +7135,7 @@
         <v>434</v>
       </c>
       <c r="M65">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7217,7 +7217,7 @@
         <v>753</v>
       </c>
       <c r="M67">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7340,7 +7340,7 @@
         <v>36</v>
       </c>
       <c r="M70">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -7381,7 +7381,7 @@
         <v>56</v>
       </c>
       <c r="M71">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -7463,7 +7463,7 @@
         <v>171</v>
       </c>
       <c r="M73">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7586,7 +7586,7 @@
         <v>348</v>
       </c>
       <c r="M76">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7668,7 +7668,7 @@
         <v>287</v>
       </c>
       <c r="M78">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7709,7 +7709,7 @@
         <v>598</v>
       </c>
       <c r="M79">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7873,7 +7873,7 @@
         <v>479</v>
       </c>
       <c r="M83">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7955,7 +7955,7 @@
         <v>1080</v>
       </c>
       <c r="M85">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7996,7 +7996,7 @@
         <v>134</v>
       </c>
       <c r="M86">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -8078,7 +8078,7 @@
         <v>223</v>
       </c>
       <c r="M88">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -8160,7 +8160,7 @@
         <v>230</v>
       </c>
       <c r="M90">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -8242,7 +8242,7 @@
         <v>66</v>
       </c>
       <c r="M92">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -8283,7 +8283,7 @@
         <v>109</v>
       </c>
       <c r="M93">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -8324,7 +8324,7 @@
         <v>259</v>
       </c>
       <c r="M94">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -8365,7 +8365,7 @@
         <v>302</v>
       </c>
       <c r="M95">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8529,7 +8529,7 @@
         <v>373</v>
       </c>
       <c r="M99">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8611,7 +8611,7 @@
         <v>21921</v>
       </c>
       <c r="M101">
-        <v>15839</v>
+        <v>15920</v>
       </c>
     </row>
   </sheetData>
@@ -9173,7 +9173,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9337,7 +9337,7 @@
         <v>753</v>
       </c>
       <c r="M7">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -9485,7 +9485,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9526,7 +9526,7 @@
         <v>48</v>
       </c>
       <c r="M4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9649,7 +9649,7 @@
         <v>539</v>
       </c>
       <c r="M7">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -9797,7 +9797,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9920,7 +9920,7 @@
         <v>106</v>
       </c>
       <c r="M6">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9961,7 +9961,7 @@
         <v>479</v>
       </c>
       <c r="M7">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -10109,7 +10109,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10273,7 +10273,7 @@
         <v>351</v>
       </c>
       <c r="M7">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -10692,7 +10692,7 @@
         <v>165</v>
       </c>
       <c r="M2">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10856,7 +10856,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10897,7 +10897,7 @@
         <v>434</v>
       </c>
       <c r="M7">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -11354,7 +11354,7 @@
         <v>26</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11453,7 +11453,7 @@
         <v>13</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11494,7 +11494,7 @@
         <v>57</v>
       </c>
       <c r="M7">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -12515,7 +12515,7 @@
         <v>67</v>
       </c>
       <c r="M3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12679,7 +12679,7 @@
         <v>348</v>
       </c>
       <c r="M7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -13209,7 +13209,7 @@
         <v>41</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13250,7 +13250,7 @@
         <v>143</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -13833,7 +13833,7 @@
         <v>62</v>
       </c>
       <c r="M6">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13874,7 +13874,7 @@
         <v>230</v>
       </c>
       <c r="M7">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -13981,7 +13981,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14022,7 +14022,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14145,7 +14145,7 @@
         <v>340</v>
       </c>
       <c r="M6">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14186,7 +14186,7 @@
         <v>1427</v>
       </c>
       <c r="M7">
-        <v>1094</v>
+        <v>1096</v>
       </c>
     </row>
   </sheetData>
@@ -14334,7 +14334,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14486,7 +14486,7 @@
         <v>167</v>
       </c>
       <c r="M7">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -14928,7 +14928,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15092,7 +15092,7 @@
         <v>187</v>
       </c>
       <c r="M7">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -15540,7 +15540,7 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15704,7 +15704,7 @@
         <v>302</v>
       </c>
       <c r="M7">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -16408,7 +16408,7 @@
         <v>242</v>
       </c>
       <c r="M2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16449,7 +16449,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16613,7 +16613,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -16881,7 +16881,7 @@
         <v>207</v>
       </c>
       <c r="M6">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16922,7 +16922,7 @@
         <v>450</v>
       </c>
       <c r="M7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -17070,7 +17070,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17234,7 +17234,7 @@
         <v>128</v>
       </c>
       <c r="M7">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -17382,7 +17382,7 @@
         <v>180</v>
       </c>
       <c r="M3">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17546,7 +17546,7 @@
         <v>593</v>
       </c>
       <c r="M7">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -17653,7 +17653,7 @@
         <v>113</v>
       </c>
       <c r="M2">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17817,7 +17817,7 @@
         <v>79</v>
       </c>
       <c r="M6">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17858,7 +17858,7 @@
         <v>373</v>
       </c>
       <c r="M7">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -18318,7 +18318,7 @@
         <v>17</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18467,7 +18467,7 @@
         <v>112</v>
       </c>
       <c r="M7">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -18615,7 +18615,7 @@
         <v>341</v>
       </c>
       <c r="M3">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18779,7 +18779,7 @@
         <v>973</v>
       </c>
       <c r="M7">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -19168,7 +19168,7 @@
         <v>51</v>
       </c>
       <c r="M2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19367,7 +19367,7 @@
         <v>192</v>
       </c>
       <c r="M7">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -20156,7 +20156,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -20252,7 +20252,7 @@
         <v>36</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -20400,7 +20400,7 @@
         <v>65</v>
       </c>
       <c r="M3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20558,7 +20558,7 @@
         <v>259</v>
       </c>
       <c r="M7">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -21650,7 +21650,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -21752,7 +21752,7 @@
         <v>134</v>
       </c>
       <c r="M7">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -21900,7 +21900,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22064,7 +22064,7 @@
         <v>223</v>
       </c>
       <c r="M7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -22326,7 +22326,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22367,7 +22367,7 @@
         <v>66</v>
       </c>
       <c r="M7">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -22515,7 +22515,7 @@
         <v>50</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22679,7 +22679,7 @@
         <v>171</v>
       </c>
       <c r="M7">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -22786,7 +22786,7 @@
         <v>84</v>
       </c>
       <c r="M2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22991,7 +22991,7 @@
         <v>213</v>
       </c>
       <c r="M7">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -23683,7 +23683,7 @@
         <v>62</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23847,7 +23847,7 @@
         <v>45</v>
       </c>
       <c r="M6">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23888,7 +23888,7 @@
         <v>190</v>
       </c>
       <c r="M7">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -25234,7 +25234,7 @@
         <v>92</v>
       </c>
       <c r="M2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25275,7 +25275,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25436,7 +25436,7 @@
         <v>272</v>
       </c>
       <c r="M7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -25543,7 +25543,7 @@
         <v>25</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25742,7 +25742,7 @@
         <v>75</v>
       </c>
       <c r="M7">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -27043,7 +27043,7 @@
         <v>38</v>
       </c>
       <c r="M2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -27239,7 +27239,7 @@
         <v>109</v>
       </c>
       <c r="M7">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -28389,7 +28389,7 @@
         <v>25</v>
       </c>
       <c r="M6">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -28430,7 +28430,7 @@
         <v>101</v>
       </c>
       <c r="M7">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -28537,7 +28537,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28578,7 +28578,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28701,7 +28701,7 @@
         <v>226</v>
       </c>
       <c r="M6">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -28742,7 +28742,7 @@
         <v>1080</v>
       </c>
       <c r="M7">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -30695,7 +30695,7 @@
         <v>11</v>
       </c>
       <c r="M4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -30812,7 +30812,7 @@
         <v>148</v>
       </c>
       <c r="M7">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -31824,7 +31824,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -31988,7 +31988,7 @@
         <v>459</v>
       </c>
       <c r="M7">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -901,7 +901,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5042</v>
+        <v>5064</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>7128</v>
       </c>
       <c r="M3">
-        <v>5655</v>
+        <v>5681</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>1958</v>
       </c>
       <c r="M4">
-        <v>1534</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>5816</v>
       </c>
       <c r="M6">
-        <v>3698</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>21926</v>
       </c>
       <c r="M7">
-        <v>16268</v>
+        <v>16335</v>
       </c>
     </row>
   </sheetData>
@@ -1830,7 +1830,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1985,7 +1985,7 @@
         <v>56</v>
       </c>
       <c r="M7">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2404,7 @@
         <v>368</v>
       </c>
       <c r="M2">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2445,7 +2445,7 @@
         <v>465</v>
       </c>
       <c r="M3">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2486,7 +2486,7 @@
         <v>66</v>
       </c>
       <c r="M4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2568,7 +2568,7 @@
         <v>286</v>
       </c>
       <c r="M6">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2609,7 +2609,7 @@
         <v>1206</v>
       </c>
       <c r="M7">
-        <v>881</v>
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -2716,7 +2716,7 @@
         <v>185</v>
       </c>
       <c r="M2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2921,7 +2921,7 @@
         <v>598</v>
       </c>
       <c r="M7">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -3069,7 +3069,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3233,7 +3233,7 @@
         <v>827</v>
       </c>
       <c r="M7">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>
@@ -3975,7 +3975,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4016,7 +4016,7 @@
         <v>52</v>
       </c>
       <c r="M4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4139,7 +4139,7 @@
         <v>682</v>
       </c>
       <c r="M7">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>
@@ -4716,7 +4716,7 @@
         <v>177</v>
       </c>
       <c r="M6">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4757,7 +4757,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4798,7 +4798,7 @@
         <v>1427</v>
       </c>
       <c r="M8">
-        <v>1121</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4839,7 +4839,7 @@
         <v>124</v>
       </c>
       <c r="M9">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4921,7 +4921,7 @@
         <v>351</v>
       </c>
       <c r="M11">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5044,7 +5044,7 @@
         <v>101</v>
       </c>
       <c r="M14">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -5249,7 +5249,7 @@
         <v>593</v>
       </c>
       <c r="M19">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5413,7 +5413,7 @@
         <v>231</v>
       </c>
       <c r="M23">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5495,7 +5495,7 @@
         <v>128</v>
       </c>
       <c r="M25">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5659,7 +5659,7 @@
         <v>1206</v>
       </c>
       <c r="M29">
-        <v>881</v>
+        <v>889</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5823,7 +5823,7 @@
         <v>973</v>
       </c>
       <c r="M33">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5987,7 +5987,7 @@
         <v>827</v>
       </c>
       <c r="M37">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6192,7 +6192,7 @@
         <v>682</v>
       </c>
       <c r="M42">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6438,7 +6438,7 @@
         <v>276</v>
       </c>
       <c r="M48">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6479,7 +6479,7 @@
         <v>112</v>
       </c>
       <c r="M49">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6561,7 +6561,7 @@
         <v>267</v>
       </c>
       <c r="M51">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6602,7 +6602,7 @@
         <v>459</v>
       </c>
       <c r="M52">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6643,7 +6643,7 @@
         <v>233</v>
       </c>
       <c r="M53">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -7053,7 +7053,7 @@
         <v>388</v>
       </c>
       <c r="M63">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7135,7 +7135,7 @@
         <v>434</v>
       </c>
       <c r="M65">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7217,7 +7217,7 @@
         <v>753</v>
       </c>
       <c r="M67">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7258,7 +7258,7 @@
         <v>67</v>
       </c>
       <c r="M68">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -7381,7 +7381,7 @@
         <v>56</v>
       </c>
       <c r="M71">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -7463,7 +7463,7 @@
         <v>171</v>
       </c>
       <c r="M73">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7545,7 +7545,7 @@
         <v>79</v>
       </c>
       <c r="M75">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -7586,7 +7586,7 @@
         <v>348</v>
       </c>
       <c r="M76">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7627,7 +7627,7 @@
         <v>143</v>
       </c>
       <c r="M77">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -7709,7 +7709,7 @@
         <v>598</v>
       </c>
       <c r="M79">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7873,7 +7873,7 @@
         <v>479</v>
       </c>
       <c r="M83">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7955,7 +7955,7 @@
         <v>1080</v>
       </c>
       <c r="M85">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -8037,7 +8037,7 @@
         <v>59</v>
       </c>
       <c r="M87">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -8078,7 +8078,7 @@
         <v>223</v>
       </c>
       <c r="M88">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -8119,7 +8119,7 @@
         <v>289</v>
       </c>
       <c r="M89">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -8160,7 +8160,7 @@
         <v>230</v>
       </c>
       <c r="M90">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -8242,7 +8242,7 @@
         <v>66</v>
       </c>
       <c r="M92">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -8283,7 +8283,7 @@
         <v>109</v>
       </c>
       <c r="M93">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -8365,7 +8365,7 @@
         <v>302</v>
       </c>
       <c r="M95">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8611,7 +8611,7 @@
         <v>21926</v>
       </c>
       <c r="M101">
-        <v>16268</v>
+        <v>16335</v>
       </c>
     </row>
   </sheetData>
@@ -9173,7 +9173,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9337,7 +9337,7 @@
         <v>753</v>
       </c>
       <c r="M7">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -9797,7 +9797,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9961,7 +9961,7 @@
         <v>479</v>
       </c>
       <c r="M7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -10068,7 +10068,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10109,7 +10109,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10273,7 +10273,7 @@
         <v>351</v>
       </c>
       <c r="M7">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -10733,7 +10733,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10897,7 +10897,7 @@
         <v>434</v>
       </c>
       <c r="M7">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -12474,7 +12474,7 @@
         <v>68</v>
       </c>
       <c r="M2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12638,7 +12638,7 @@
         <v>159</v>
       </c>
       <c r="M6">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12679,7 +12679,7 @@
         <v>348</v>
       </c>
       <c r="M7">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -13357,7 +13357,7 @@
         <v>71</v>
       </c>
       <c r="M2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13562,7 +13562,7 @@
         <v>233</v>
       </c>
       <c r="M7">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -13669,7 +13669,7 @@
         <v>77</v>
       </c>
       <c r="M2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13710,7 +13710,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13874,7 +13874,7 @@
         <v>230</v>
       </c>
       <c r="M7">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -13981,7 +13981,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14022,7 +14022,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14063,7 +14063,7 @@
         <v>104</v>
       </c>
       <c r="M4">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14145,7 +14145,7 @@
         <v>340</v>
       </c>
       <c r="M6">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14186,7 +14186,7 @@
         <v>1427</v>
       </c>
       <c r="M7">
-        <v>1121</v>
+        <v>1127</v>
       </c>
     </row>
   </sheetData>
@@ -15281,7 +15281,7 @@
         <v>56</v>
       </c>
       <c r="M4">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15392,7 +15392,7 @@
         <v>276</v>
       </c>
       <c r="M7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -15499,7 +15499,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15704,7 +15704,7 @@
         <v>302</v>
       </c>
       <c r="M7">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -15811,7 +15811,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16016,7 +16016,7 @@
         <v>177</v>
       </c>
       <c r="M7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -16490,7 +16490,7 @@
         <v>43</v>
       </c>
       <c r="M4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -16572,7 +16572,7 @@
         <v>166</v>
       </c>
       <c r="M6">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16613,7 +16613,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -17193,7 +17193,7 @@
         <v>19</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17234,7 +17234,7 @@
         <v>128</v>
       </c>
       <c r="M7">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -17382,7 +17382,7 @@
         <v>180</v>
       </c>
       <c r="M3">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17546,7 +17546,7 @@
         <v>593</v>
       </c>
       <c r="M7">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -17965,7 +17965,7 @@
         <v>50</v>
       </c>
       <c r="M2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18006,7 +18006,7 @@
         <v>47</v>
       </c>
       <c r="M3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18170,7 +18170,7 @@
         <v>143</v>
       </c>
       <c r="M7">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -18426,7 +18426,7 @@
         <v>45</v>
       </c>
       <c r="M6">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18467,7 +18467,7 @@
         <v>112</v>
       </c>
       <c r="M7">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -18615,7 +18615,7 @@
         <v>341</v>
       </c>
       <c r="M3">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18656,7 +18656,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18779,7 +18779,7 @@
         <v>973</v>
       </c>
       <c r="M7">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -19803,7 +19803,7 @@
         <v>79</v>
       </c>
       <c r="M3">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19926,7 +19926,7 @@
         <v>57</v>
       </c>
       <c r="M6">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19967,7 +19967,7 @@
         <v>267</v>
       </c>
       <c r="M7">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -21859,7 +21859,7 @@
         <v>66</v>
       </c>
       <c r="M2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22064,7 +22064,7 @@
         <v>223</v>
       </c>
       <c r="M7">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -22212,7 +22212,7 @@
         <v>13</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22367,7 +22367,7 @@
         <v>66</v>
       </c>
       <c r="M7">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -22474,7 +22474,7 @@
         <v>61</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22679,7 +22679,7 @@
         <v>171</v>
       </c>
       <c r="M7">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -23139,7 +23139,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23288,7 +23288,7 @@
         <v>67</v>
       </c>
       <c r="M7">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -25540,7 +25540,7 @@
         <v>40</v>
       </c>
       <c r="M2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25581,7 +25581,7 @@
         <v>45</v>
       </c>
       <c r="M3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25745,7 +25745,7 @@
         <v>124</v>
       </c>
       <c r="M7">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -25893,7 +25893,7 @@
         <v>86</v>
       </c>
       <c r="M3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26054,7 +26054,7 @@
         <v>289</v>
       </c>
       <c r="M7">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -27043,7 +27043,7 @@
         <v>38</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -27239,7 +27239,7 @@
         <v>109</v>
       </c>
       <c r="M7">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -27498,7 +27498,7 @@
         <v>20</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -27539,7 +27539,7 @@
         <v>59</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -27922,7 +27922,7 @@
         <v>59</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28127,7 +28127,7 @@
         <v>231</v>
       </c>
       <c r="M7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -28316,7 +28316,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -28430,7 +28430,7 @@
         <v>101</v>
       </c>
       <c r="M7">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -28537,7 +28537,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28701,7 +28701,7 @@
         <v>226</v>
       </c>
       <c r="M6">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -28742,7 +28742,7 @@
         <v>1080</v>
       </c>
       <c r="M7">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
   </sheetData>
@@ -30192,7 +30192,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -30233,7 +30233,7 @@
         <v>79</v>
       </c>
       <c r="M7">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -31783,7 +31783,7 @@
         <v>145</v>
       </c>
       <c r="M2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31947,7 +31947,7 @@
         <v>127</v>
       </c>
       <c r="M6">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -31988,7 +31988,7 @@
         <v>459</v>
       </c>
       <c r="M7">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -901,7 +901,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5064</v>
+        <v>5081</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -930,7 +930,7 @@
         <v>8363</v>
       </c>
       <c r="I3">
-        <v>7508</v>
+        <v>7509</v>
       </c>
       <c r="J3">
         <v>8099</v>
@@ -942,7 +942,7 @@
         <v>7128</v>
       </c>
       <c r="M3">
-        <v>5681</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -971,7 +971,7 @@
         <v>1886</v>
       </c>
       <c r="I4">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="J4">
         <v>2043</v>
@@ -980,10 +980,10 @@
         <v>1958</v>
       </c>
       <c r="L4">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="M4">
-        <v>1539</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>436</v>
       </c>
       <c r="M5">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>5816</v>
       </c>
       <c r="M6">
-        <v>3712</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1094,7 +1094,7 @@
         <v>26221</v>
       </c>
       <c r="I7">
-        <v>26486</v>
+        <v>26488</v>
       </c>
       <c r="J7">
         <v>29550</v>
@@ -1103,10 +1103,10 @@
         <v>27768</v>
       </c>
       <c r="L7">
-        <v>21926</v>
+        <v>21927</v>
       </c>
       <c r="M7">
-        <v>16335</v>
+        <v>16392</v>
       </c>
     </row>
   </sheetData>
@@ -1254,7 +1254,7 @@
         <v>93</v>
       </c>
       <c r="M3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1418,7 +1418,7 @@
         <v>287</v>
       </c>
       <c r="M7">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -2445,7 +2445,7 @@
         <v>465</v>
       </c>
       <c r="M3">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2609,7 +2609,7 @@
         <v>1206</v>
       </c>
       <c r="M7">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -2839,7 +2839,7 @@
         <v>18</v>
       </c>
       <c r="M5">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2921,7 +2921,7 @@
         <v>598</v>
       </c>
       <c r="M7">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -3934,7 +3934,7 @@
         <v>187</v>
       </c>
       <c r="M2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3975,7 +3975,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4139,7 +4139,7 @@
         <v>682</v>
       </c>
       <c r="M7">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
@@ -4552,7 +4552,7 @@
         <v>190</v>
       </c>
       <c r="M2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4716,7 +4716,7 @@
         <v>177</v>
       </c>
       <c r="M6">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4757,7 +4757,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4798,7 +4798,7 @@
         <v>1427</v>
       </c>
       <c r="M8">
-        <v>1127</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4839,7 +4839,7 @@
         <v>124</v>
       </c>
       <c r="M9">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4921,7 +4921,7 @@
         <v>351</v>
       </c>
       <c r="M11">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5331,7 +5331,7 @@
         <v>69</v>
       </c>
       <c r="M21">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -5577,7 +5577,7 @@
         <v>192</v>
       </c>
       <c r="M27">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5659,7 +5659,7 @@
         <v>1206</v>
       </c>
       <c r="M29">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5823,7 +5823,7 @@
         <v>973</v>
       </c>
       <c r="M33">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -6151,7 +6151,7 @@
         <v>92</v>
       </c>
       <c r="M41">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -6192,7 +6192,7 @@
         <v>682</v>
       </c>
       <c r="M42">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6274,7 +6274,7 @@
         <v>148</v>
       </c>
       <c r="M44">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -6397,7 +6397,7 @@
         <v>151</v>
       </c>
       <c r="M47">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6438,7 +6438,7 @@
         <v>276</v>
       </c>
       <c r="M48">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6479,7 +6479,7 @@
         <v>112</v>
       </c>
       <c r="M49">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6561,7 +6561,7 @@
         <v>267</v>
       </c>
       <c r="M51">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6643,7 +6643,7 @@
         <v>233</v>
       </c>
       <c r="M53">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6684,7 +6684,7 @@
         <v>450</v>
       </c>
       <c r="M54">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6725,7 +6725,7 @@
         <v>227</v>
       </c>
       <c r="M55">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6807,7 +6807,7 @@
         <v>75</v>
       </c>
       <c r="M57">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -7041,7 +7041,7 @@
         <v>454</v>
       </c>
       <c r="I63">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J63">
         <v>423</v>
@@ -7050,10 +7050,10 @@
         <v>369</v>
       </c>
       <c r="L63">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M63">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7135,7 +7135,7 @@
         <v>434</v>
       </c>
       <c r="M65">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7217,7 +7217,7 @@
         <v>753</v>
       </c>
       <c r="M67">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7299,7 +7299,7 @@
         <v>47</v>
       </c>
       <c r="M69">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -7504,7 +7504,7 @@
         <v>19</v>
       </c>
       <c r="M74">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -7668,7 +7668,7 @@
         <v>287</v>
       </c>
       <c r="M78">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7709,7 +7709,7 @@
         <v>598</v>
       </c>
       <c r="M79">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7914,7 +7914,7 @@
         <v>208</v>
       </c>
       <c r="M84">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7955,7 +7955,7 @@
         <v>1080</v>
       </c>
       <c r="M85">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -8119,7 +8119,7 @@
         <v>289</v>
       </c>
       <c r="M89">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -8160,7 +8160,7 @@
         <v>230</v>
       </c>
       <c r="M90">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -8242,7 +8242,7 @@
         <v>66</v>
       </c>
       <c r="M92">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -8324,7 +8324,7 @@
         <v>259</v>
       </c>
       <c r="M94">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -8365,7 +8365,7 @@
         <v>302</v>
       </c>
       <c r="M95">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8488,7 +8488,7 @@
         <v>113</v>
       </c>
       <c r="M98">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -8529,7 +8529,7 @@
         <v>373</v>
       </c>
       <c r="M99">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8599,7 +8599,7 @@
         <v>26221</v>
       </c>
       <c r="I101">
-        <v>26486</v>
+        <v>26488</v>
       </c>
       <c r="J101">
         <v>29550</v>
@@ -8608,10 +8608,10 @@
         <v>27768</v>
       </c>
       <c r="L101">
-        <v>21926</v>
+        <v>21927</v>
       </c>
       <c r="M101">
-        <v>16335</v>
+        <v>16392</v>
       </c>
     </row>
   </sheetData>
@@ -8861,7 +8861,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9025,7 +9025,7 @@
         <v>227</v>
       </c>
       <c r="M7">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -9255,7 +9255,7 @@
         <v>21</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9337,7 +9337,7 @@
         <v>753</v>
       </c>
       <c r="M7">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -10068,7 +10068,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10273,7 +10273,7 @@
         <v>351</v>
       </c>
       <c r="M7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -10733,7 +10733,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10856,7 +10856,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10897,7 +10897,7 @@
         <v>434</v>
       </c>
       <c r="M7">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -11753,7 +11753,7 @@
         <v>50</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11794,7 +11794,7 @@
         <v>113</v>
       </c>
       <c r="M7">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -13521,7 +13521,7 @@
         <v>77</v>
       </c>
       <c r="M6">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13562,7 +13562,7 @@
         <v>233</v>
       </c>
       <c r="M7">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -13669,7 +13669,7 @@
         <v>77</v>
       </c>
       <c r="M2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13710,7 +13710,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13751,7 +13751,7 @@
         <v>19</v>
       </c>
       <c r="M4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13874,7 +13874,7 @@
         <v>230</v>
       </c>
       <c r="M7">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -13981,7 +13981,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14063,7 +14063,7 @@
         <v>104</v>
       </c>
       <c r="M4">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14145,7 +14145,7 @@
         <v>340</v>
       </c>
       <c r="M6">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14186,7 +14186,7 @@
         <v>1427</v>
       </c>
       <c r="M7">
-        <v>1127</v>
+        <v>1131</v>
       </c>
     </row>
   </sheetData>
@@ -15281,7 +15281,7 @@
         <v>56</v>
       </c>
       <c r="M4">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15351,7 +15351,7 @@
         <v>110</v>
       </c>
       <c r="M6">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15392,7 +15392,7 @@
         <v>276</v>
       </c>
       <c r="M7">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -15540,7 +15540,7 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15704,7 +15704,7 @@
         <v>302</v>
       </c>
       <c r="M7">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -15811,7 +15811,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16016,7 +16016,7 @@
         <v>177</v>
       </c>
       <c r="M7">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -16260,7 +16260,7 @@
         <v>34</v>
       </c>
       <c r="M6">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16301,7 +16301,7 @@
         <v>69</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -16408,7 +16408,7 @@
         <v>242</v>
       </c>
       <c r="M2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16613,7 +16613,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -16720,7 +16720,7 @@
         <v>85</v>
       </c>
       <c r="M2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16761,7 +16761,7 @@
         <v>115</v>
       </c>
       <c r="M3">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16922,7 +16922,7 @@
         <v>450</v>
       </c>
       <c r="M7">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -17653,7 +17653,7 @@
         <v>113</v>
       </c>
       <c r="M2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17858,7 +17858,7 @@
         <v>373</v>
       </c>
       <c r="M7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -18426,7 +18426,7 @@
         <v>45</v>
       </c>
       <c r="M6">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18467,7 +18467,7 @@
         <v>112</v>
       </c>
       <c r="M7">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -18574,7 +18574,7 @@
         <v>265</v>
       </c>
       <c r="M2">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18656,7 +18656,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18779,7 +18779,7 @@
         <v>973</v>
       </c>
       <c r="M7">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -19168,7 +19168,7 @@
         <v>51</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19367,7 +19367,7 @@
         <v>192</v>
       </c>
       <c r="M7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -19803,7 +19803,7 @@
         <v>79</v>
       </c>
       <c r="M3">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19926,7 +19926,7 @@
         <v>57</v>
       </c>
       <c r="M6">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19967,7 +19967,7 @@
         <v>267</v>
       </c>
       <c r="M7">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -20359,7 +20359,7 @@
         <v>62</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20400,7 +20400,7 @@
         <v>65</v>
       </c>
       <c r="M3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20558,7 +20558,7 @@
         <v>259</v>
       </c>
       <c r="M7">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -22326,7 +22326,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22367,7 +22367,7 @@
         <v>66</v>
       </c>
       <c r="M7">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -23847,7 +23847,7 @@
         <v>45</v>
       </c>
       <c r="M6">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23888,7 +23888,7 @@
         <v>190</v>
       </c>
       <c r="M7">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -24777,7 +24777,7 @@
         <v>58</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24818,7 +24818,7 @@
         <v>208</v>
       </c>
       <c r="M7">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -24966,7 +24966,7 @@
         <v>21</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25124,7 +25124,7 @@
         <v>75</v>
       </c>
       <c r="M7">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -25704,7 +25704,7 @@
         <v>30</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25745,7 +25745,7 @@
         <v>124</v>
       </c>
       <c r="M7">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -25852,7 +25852,7 @@
         <v>75</v>
       </c>
       <c r="M2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25893,7 +25893,7 @@
         <v>86</v>
       </c>
       <c r="M3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26054,7 +26054,7 @@
         <v>289</v>
       </c>
       <c r="M7">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -26437,7 +26437,7 @@
         <v>56</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26636,7 +26636,7 @@
         <v>151</v>
       </c>
       <c r="M7">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -26784,7 +26784,7 @@
         <v>28</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26936,7 +26936,7 @@
         <v>92</v>
       </c>
       <c r="M7">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -28537,7 +28537,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28578,7 +28578,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28619,7 +28619,7 @@
         <v>66</v>
       </c>
       <c r="M4">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -28701,7 +28701,7 @@
         <v>226</v>
       </c>
       <c r="M6">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -28742,7 +28742,7 @@
         <v>1080</v>
       </c>
       <c r="M7">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
   </sheetData>
@@ -29152,7 +29152,7 @@
         <v>20</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -29339,7 +29339,7 @@
         <v>47</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -30771,7 +30771,7 @@
         <v>37</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -30812,7 +30812,7 @@
         <v>148</v>
       </c>
       <c r="M7">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -32095,7 +32095,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -32261,7 +32261,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -901,7 +901,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5137</v>
+        <v>5152</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>7129</v>
       </c>
       <c r="M3">
-        <v>5759</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -968,7 +968,7 @@
         <v>1628</v>
       </c>
       <c r="H4">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="I4">
         <v>1996</v>
@@ -980,10 +980,10 @@
         <v>1958</v>
       </c>
       <c r="L4">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="M4">
-        <v>1567</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>5816</v>
       </c>
       <c r="M6">
-        <v>3752</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>24873</v>
       </c>
       <c r="H7">
-        <v>26221</v>
+        <v>26222</v>
       </c>
       <c r="I7">
         <v>26488</v>
@@ -1103,10 +1103,10 @@
         <v>27768</v>
       </c>
       <c r="L7">
-        <v>21929</v>
+        <v>21930</v>
       </c>
       <c r="M7">
-        <v>16559</v>
+        <v>16612</v>
       </c>
     </row>
   </sheetData>
@@ -2133,7 +2133,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2297,7 +2297,7 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2404,7 @@
         <v>368</v>
       </c>
       <c r="M2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2609,7 +2609,7 @@
         <v>1207</v>
       </c>
       <c r="M7">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -3028,7 +3028,7 @@
         <v>249</v>
       </c>
       <c r="M2">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3069,7 +3069,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3233,7 +3233,7 @@
         <v>827</v>
       </c>
       <c r="M7">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -3381,7 +3381,7 @@
         <v>131</v>
       </c>
       <c r="M3">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>296</v>
       </c>
       <c r="M7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -4552,7 +4552,7 @@
         <v>190</v>
       </c>
       <c r="M2">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4757,7 +4757,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4798,7 +4798,7 @@
         <v>1427</v>
       </c>
       <c r="M8">
-        <v>1138</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4880,7 +4880,7 @@
         <v>143</v>
       </c>
       <c r="M10">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4921,7 +4921,7 @@
         <v>351</v>
       </c>
       <c r="M11">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4962,7 +4962,7 @@
         <v>51</v>
       </c>
       <c r="M12">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -5044,7 +5044,7 @@
         <v>101</v>
       </c>
       <c r="M14">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -5249,7 +5249,7 @@
         <v>593</v>
       </c>
       <c r="M19">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5290,7 +5290,7 @@
         <v>541</v>
       </c>
       <c r="M20">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5454,7 +5454,7 @@
         <v>68</v>
       </c>
       <c r="M24">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5659,7 +5659,7 @@
         <v>1207</v>
       </c>
       <c r="M29">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5987,7 +5987,7 @@
         <v>827</v>
       </c>
       <c r="M37">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6479,7 +6479,7 @@
         <v>112</v>
       </c>
       <c r="M49">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6561,7 +6561,7 @@
         <v>267</v>
       </c>
       <c r="M51">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6602,7 +6602,7 @@
         <v>459</v>
       </c>
       <c r="M52">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6725,7 +6725,7 @@
         <v>227</v>
       </c>
       <c r="M55">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6930,7 +6930,7 @@
         <v>144</v>
       </c>
       <c r="M60">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -7038,7 +7038,7 @@
         <v>439</v>
       </c>
       <c r="H63">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I63">
         <v>432</v>
@@ -7050,10 +7050,10 @@
         <v>369</v>
       </c>
       <c r="L63">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M63">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7135,7 +7135,7 @@
         <v>434</v>
       </c>
       <c r="M65">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7176,7 +7176,7 @@
         <v>62</v>
       </c>
       <c r="M66">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -7217,7 +7217,7 @@
         <v>753</v>
       </c>
       <c r="M67">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7463,7 +7463,7 @@
         <v>171</v>
       </c>
       <c r="M73">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7586,7 +7586,7 @@
         <v>348</v>
       </c>
       <c r="M76">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7627,7 +7627,7 @@
         <v>143</v>
       </c>
       <c r="M77">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -7750,7 +7750,7 @@
         <v>69</v>
       </c>
       <c r="M80">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -7873,7 +7873,7 @@
         <v>479</v>
       </c>
       <c r="M83">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7955,7 +7955,7 @@
         <v>1080</v>
       </c>
       <c r="M85">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7996,7 +7996,7 @@
         <v>134</v>
       </c>
       <c r="M86">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -8078,7 +8078,7 @@
         <v>223</v>
       </c>
       <c r="M88">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -8160,7 +8160,7 @@
         <v>230</v>
       </c>
       <c r="M90">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -8201,7 +8201,7 @@
         <v>296</v>
       </c>
       <c r="M91">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -8283,7 +8283,7 @@
         <v>109</v>
       </c>
       <c r="M93">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -8324,7 +8324,7 @@
         <v>259</v>
       </c>
       <c r="M94">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -8406,7 +8406,7 @@
         <v>240</v>
       </c>
       <c r="M96">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -8529,7 +8529,7 @@
         <v>373</v>
       </c>
       <c r="M99">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8596,7 +8596,7 @@
         <v>24873</v>
       </c>
       <c r="H101">
-        <v>26221</v>
+        <v>26222</v>
       </c>
       <c r="I101">
         <v>26488</v>
@@ -8608,10 +8608,10 @@
         <v>27768</v>
       </c>
       <c r="L101">
-        <v>21929</v>
+        <v>21930</v>
       </c>
       <c r="M101">
-        <v>16559</v>
+        <v>16612</v>
       </c>
     </row>
   </sheetData>
@@ -8861,7 +8861,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8984,7 +8984,7 @@
         <v>62</v>
       </c>
       <c r="M6">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9025,7 +9025,7 @@
         <v>227</v>
       </c>
       <c r="M7">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -9214,7 +9214,7 @@
         <v>51</v>
       </c>
       <c r="M4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9337,7 +9337,7 @@
         <v>753</v>
       </c>
       <c r="M7">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -9485,7 +9485,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9526,7 +9526,7 @@
         <v>49</v>
       </c>
       <c r="M4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9649,7 +9649,7 @@
         <v>541</v>
       </c>
       <c r="M7">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -9797,7 +9797,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9961,7 +9961,7 @@
         <v>479</v>
       </c>
       <c r="M7">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -10068,7 +10068,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10109,7 +10109,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10150,7 +10150,7 @@
         <v>26</v>
       </c>
       <c r="M4">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10273,7 +10273,7 @@
         <v>351</v>
       </c>
       <c r="M7">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -10856,7 +10856,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10897,7 +10897,7 @@
         <v>434</v>
       </c>
       <c r="M7">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -12638,7 +12638,7 @@
         <v>159</v>
       </c>
       <c r="M6">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12679,7 +12679,7 @@
         <v>348</v>
       </c>
       <c r="M7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -13209,7 +13209,7 @@
         <v>41</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13250,7 +13250,7 @@
         <v>143</v>
       </c>
       <c r="M7">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -13669,7 +13669,7 @@
         <v>77</v>
       </c>
       <c r="M2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13874,7 +13874,7 @@
         <v>230</v>
       </c>
       <c r="M7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -14022,7 +14022,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14063,7 +14063,7 @@
         <v>104</v>
       </c>
       <c r="M4">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14145,7 +14145,7 @@
         <v>340</v>
       </c>
       <c r="M6">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14186,7 +14186,7 @@
         <v>1427</v>
       </c>
       <c r="M7">
-        <v>1138</v>
+        <v>1144</v>
       </c>
     </row>
   </sheetData>
@@ -16408,7 +16408,7 @@
         <v>242</v>
       </c>
       <c r="M2">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16449,7 +16449,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16613,7 +16613,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -17341,7 +17341,7 @@
         <v>211</v>
       </c>
       <c r="M2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17546,7 +17546,7 @@
         <v>593</v>
       </c>
       <c r="M7">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -17653,7 +17653,7 @@
         <v>113</v>
       </c>
       <c r="M2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17694,7 +17694,7 @@
         <v>150</v>
       </c>
       <c r="M3">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17817,7 +17817,7 @@
         <v>79</v>
       </c>
       <c r="M6">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17858,7 +17858,7 @@
         <v>373</v>
       </c>
       <c r="M7">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -18006,7 +18006,7 @@
         <v>47</v>
       </c>
       <c r="M3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18170,7 +18170,7 @@
         <v>143</v>
       </c>
       <c r="M7">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -18277,7 +18277,7 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18467,7 +18467,7 @@
         <v>112</v>
       </c>
       <c r="M7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -19515,7 +19515,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19655,7 +19655,7 @@
         <v>51</v>
       </c>
       <c r="M7">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -19762,7 +19762,7 @@
         <v>83</v>
       </c>
       <c r="M2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19967,7 +19967,7 @@
         <v>267</v>
       </c>
       <c r="M7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -20441,7 +20441,7 @@
         <v>32</v>
       </c>
       <c r="M4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -20558,7 +20558,7 @@
         <v>259</v>
       </c>
       <c r="M7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -21650,7 +21650,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -21752,7 +21752,7 @@
         <v>134</v>
       </c>
       <c r="M7">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -21859,7 +21859,7 @@
         <v>66</v>
       </c>
       <c r="M2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21900,7 +21900,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22064,7 +22064,7 @@
         <v>223</v>
       </c>
       <c r="M7">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -22474,7 +22474,7 @@
         <v>61</v>
       </c>
       <c r="M2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22679,7 +22679,7 @@
         <v>171</v>
       </c>
       <c r="M7">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -23724,7 +23724,7 @@
         <v>63</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23888,7 +23888,7 @@
         <v>190</v>
       </c>
       <c r="M7">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -24465,7 +24465,7 @@
         <v>38</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24506,7 +24506,7 @@
         <v>144</v>
       </c>
       <c r="M7">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -26437,7 +26437,7 @@
         <v>56</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26519,7 +26519,7 @@
         <v>12</v>
       </c>
       <c r="M4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -27198,7 +27198,7 @@
         <v>32</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -27239,7 +27239,7 @@
         <v>109</v>
       </c>
       <c r="M7">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -28234,7 +28234,7 @@
         <v>44</v>
       </c>
       <c r="M2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28430,7 +28430,7 @@
         <v>101</v>
       </c>
       <c r="M7">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -28537,7 +28537,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28578,7 +28578,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28742,7 +28742,7 @@
         <v>1080</v>
       </c>
       <c r="M7">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -31280,7 +31280,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -31379,7 +31379,7 @@
         <v>62</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -31568,7 +31568,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -31676,7 +31676,7 @@
         <v>68</v>
       </c>
       <c r="M7">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -31824,7 +31824,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -31988,7 +31988,7 @@
         <v>459</v>
       </c>
       <c r="M7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -32505,7 +32505,7 @@
         <v>35</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -32546,7 +32546,7 @@
         <v>69</v>
       </c>
       <c r="M7">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -901,7 +901,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5152</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>7129</v>
       </c>
       <c r="M3">
-        <v>5780</v>
+        <v>5796</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -959,13 +959,13 @@
         <v>2025</v>
       </c>
       <c r="E4">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="F4">
         <v>2029</v>
       </c>
       <c r="G4">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="H4">
         <v>1887</v>
@@ -980,10 +980,10 @@
         <v>1958</v>
       </c>
       <c r="L4">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="M4">
-        <v>1574</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>436</v>
       </c>
       <c r="M5">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>5816</v>
       </c>
       <c r="M6">
-        <v>3762</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1082,13 +1082,13 @@
         <v>28215</v>
       </c>
       <c r="E7">
-        <v>26105</v>
+        <v>26106</v>
       </c>
       <c r="F7">
         <v>24233</v>
       </c>
       <c r="G7">
-        <v>24873</v>
+        <v>24874</v>
       </c>
       <c r="H7">
         <v>26222</v>
@@ -1103,10 +1103,10 @@
         <v>27768</v>
       </c>
       <c r="L7">
-        <v>21930</v>
+        <v>21929</v>
       </c>
       <c r="M7">
-        <v>16612</v>
+        <v>16669</v>
       </c>
     </row>
   </sheetData>
@@ -2445,7 +2445,7 @@
         <v>466</v>
       </c>
       <c r="M3">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2486,7 +2486,7 @@
         <v>66</v>
       </c>
       <c r="M4">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2609,7 +2609,7 @@
         <v>1207</v>
       </c>
       <c r="M7">
-        <v>900</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -3028,7 +3028,7 @@
         <v>249</v>
       </c>
       <c r="M2">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3192,7 +3192,7 @@
         <v>209</v>
       </c>
       <c r="M6">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3233,7 +3233,7 @@
         <v>827</v>
       </c>
       <c r="M7">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -3340,7 +3340,7 @@
         <v>101</v>
       </c>
       <c r="M2">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3504,7 +3504,7 @@
         <v>39</v>
       </c>
       <c r="M6">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>296</v>
       </c>
       <c r="M7">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3975,7 +3975,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4016,7 +4016,7 @@
         <v>52</v>
       </c>
       <c r="M4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4098,7 +4098,7 @@
         <v>190</v>
       </c>
       <c r="M6">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4139,7 +4139,7 @@
         <v>682</v>
       </c>
       <c r="M7">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -4757,7 +4757,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4798,7 +4798,7 @@
         <v>1427</v>
       </c>
       <c r="M8">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4880,7 +4880,7 @@
         <v>143</v>
       </c>
       <c r="M10">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4921,7 +4921,7 @@
         <v>351</v>
       </c>
       <c r="M11">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5126,7 +5126,7 @@
         <v>50</v>
       </c>
       <c r="M16">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -5290,7 +5290,7 @@
         <v>541</v>
       </c>
       <c r="M20">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5659,7 +5659,7 @@
         <v>1207</v>
       </c>
       <c r="M29">
-        <v>900</v>
+        <v>904</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5741,7 +5741,7 @@
         <v>213</v>
       </c>
       <c r="M31">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5823,7 +5823,7 @@
         <v>973</v>
       </c>
       <c r="M33">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5946,7 +5946,7 @@
         <v>272</v>
       </c>
       <c r="M36">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5987,7 +5987,7 @@
         <v>827</v>
       </c>
       <c r="M37">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6192,7 +6192,7 @@
         <v>682</v>
       </c>
       <c r="M42">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6397,7 +6397,7 @@
         <v>151</v>
       </c>
       <c r="M47">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6561,7 +6561,7 @@
         <v>267</v>
       </c>
       <c r="M51">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6602,7 +6602,7 @@
         <v>459</v>
       </c>
       <c r="M52">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6684,7 +6684,7 @@
         <v>450</v>
       </c>
       <c r="M54">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -7029,13 +7029,13 @@
         <v>404</v>
       </c>
       <c r="E63">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F63">
         <v>324</v>
       </c>
       <c r="G63">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H63">
         <v>455</v>
@@ -7053,7 +7053,7 @@
         <v>390</v>
       </c>
       <c r="M63">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7135,7 +7135,7 @@
         <v>434</v>
       </c>
       <c r="M65">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7214,10 +7214,10 @@
         <v>1072</v>
       </c>
       <c r="L67">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="M67">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7586,7 +7586,7 @@
         <v>348</v>
       </c>
       <c r="M76">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7873,7 +7873,7 @@
         <v>479</v>
       </c>
       <c r="M83">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7914,7 +7914,7 @@
         <v>208</v>
       </c>
       <c r="M84">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7955,7 +7955,7 @@
         <v>1080</v>
       </c>
       <c r="M85">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -8201,7 +8201,7 @@
         <v>296</v>
       </c>
       <c r="M91">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -8324,7 +8324,7 @@
         <v>259</v>
       </c>
       <c r="M94">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -8365,7 +8365,7 @@
         <v>302</v>
       </c>
       <c r="M95">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8488,7 +8488,7 @@
         <v>113</v>
       </c>
       <c r="M98">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -8529,7 +8529,7 @@
         <v>373</v>
       </c>
       <c r="M99">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8587,13 +8587,13 @@
         <v>28215</v>
       </c>
       <c r="E101">
-        <v>26105</v>
+        <v>26106</v>
       </c>
       <c r="F101">
         <v>24233</v>
       </c>
       <c r="G101">
-        <v>24873</v>
+        <v>24874</v>
       </c>
       <c r="H101">
         <v>26222</v>
@@ -8608,10 +8608,10 @@
         <v>27768</v>
       </c>
       <c r="L101">
-        <v>21930</v>
+        <v>21929</v>
       </c>
       <c r="M101">
-        <v>16612</v>
+        <v>16669</v>
       </c>
     </row>
   </sheetData>
@@ -9173,7 +9173,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9211,7 +9211,7 @@
         <v>61</v>
       </c>
       <c r="L4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M4">
         <v>37</v>
@@ -9334,10 +9334,10 @@
         <v>1072</v>
       </c>
       <c r="L7">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="M7">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -9444,7 +9444,7 @@
         <v>170</v>
       </c>
       <c r="M2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9485,7 +9485,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9567,7 +9567,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9608,7 +9608,7 @@
         <v>123</v>
       </c>
       <c r="M6">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9649,7 +9649,7 @@
         <v>541</v>
       </c>
       <c r="M7">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -9797,7 +9797,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9961,7 +9961,7 @@
         <v>479</v>
       </c>
       <c r="M7">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -10068,7 +10068,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10109,7 +10109,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10273,7 +10273,7 @@
         <v>351</v>
       </c>
       <c r="M7">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -10692,7 +10692,7 @@
         <v>165</v>
       </c>
       <c r="M2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10856,7 +10856,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10897,7 +10897,7 @@
         <v>434</v>
       </c>
       <c r="M7">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -11642,7 +11642,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11794,7 +11794,7 @@
         <v>113</v>
       </c>
       <c r="M7">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -12638,7 +12638,7 @@
         <v>159</v>
       </c>
       <c r="M6">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12679,7 +12679,7 @@
         <v>348</v>
       </c>
       <c r="M7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -13209,7 +13209,7 @@
         <v>41</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13250,7 +13250,7 @@
         <v>143</v>
       </c>
       <c r="M7">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -13981,7 +13981,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14022,7 +14022,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14063,7 +14063,7 @@
         <v>104</v>
       </c>
       <c r="M4">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14145,7 +14145,7 @@
         <v>340</v>
       </c>
       <c r="M6">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14186,7 +14186,7 @@
         <v>1427</v>
       </c>
       <c r="M7">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
   </sheetData>
@@ -15499,7 +15499,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15704,7 +15704,7 @@
         <v>302</v>
       </c>
       <c r="M7">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -16449,7 +16449,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16572,7 +16572,7 @@
         <v>166</v>
       </c>
       <c r="M6">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16613,7 +16613,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -16802,7 +16802,7 @@
         <v>38</v>
       </c>
       <c r="M4">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -16922,7 +16922,7 @@
         <v>450</v>
       </c>
       <c r="M7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -17817,7 +17817,7 @@
         <v>79</v>
       </c>
       <c r="M6">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17858,7 +17858,7 @@
         <v>373</v>
       </c>
       <c r="M7">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -18697,7 +18697,7 @@
         <v>25</v>
       </c>
       <c r="M5">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -18779,7 +18779,7 @@
         <v>973</v>
       </c>
       <c r="M7">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -19803,7 +19803,7 @@
         <v>79</v>
       </c>
       <c r="M3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19844,7 +19844,7 @@
         <v>41</v>
       </c>
       <c r="M4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -19967,7 +19967,7 @@
         <v>267</v>
       </c>
       <c r="M7">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -20400,7 +20400,7 @@
         <v>65</v>
       </c>
       <c r="M3">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20558,7 +20558,7 @@
         <v>259</v>
       </c>
       <c r="M7">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -21108,7 +21108,7 @@
         <v>30</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21149,7 +21149,7 @@
         <v>50</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -22786,7 +22786,7 @@
         <v>84</v>
       </c>
       <c r="M2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22991,7 +22991,7 @@
         <v>213</v>
       </c>
       <c r="M7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -24613,7 +24613,7 @@
         <v>70</v>
       </c>
       <c r="M2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24818,7 +24818,7 @@
         <v>208</v>
       </c>
       <c r="M7">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -25272,7 +25272,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25433,7 +25433,7 @@
         <v>272</v>
       </c>
       <c r="M7">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -26437,7 +26437,7 @@
         <v>56</v>
       </c>
       <c r="M2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26636,7 +26636,7 @@
         <v>151</v>
       </c>
       <c r="M7">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -28537,7 +28537,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28578,7 +28578,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28742,7 +28742,7 @@
         <v>1080</v>
       </c>
       <c r="M7">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
   </sheetData>
@@ -31783,7 +31783,7 @@
         <v>145</v>
       </c>
       <c r="M2">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31988,7 +31988,7 @@
         <v>459</v>
       </c>
       <c r="M7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -901,7 +901,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5168</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>7129</v>
       </c>
       <c r="M3">
-        <v>5796</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>1960</v>
       </c>
       <c r="M4">
-        <v>1584</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>436</v>
       </c>
       <c r="M5">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>5816</v>
       </c>
       <c r="M6">
-        <v>3775</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>21929</v>
       </c>
       <c r="M7">
-        <v>16669</v>
+        <v>16742</v>
       </c>
     </row>
   </sheetData>
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1985,7 +1985,7 @@
         <v>56</v>
       </c>
       <c r="M7">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2404,7 @@
         <v>368</v>
       </c>
       <c r="M2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2445,7 +2445,7 @@
         <v>466</v>
       </c>
       <c r="M3">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2568,7 +2568,7 @@
         <v>286</v>
       </c>
       <c r="M6">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2609,7 +2609,7 @@
         <v>1207</v>
       </c>
       <c r="M7">
-        <v>904</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>
@@ -2716,7 +2716,7 @@
         <v>185</v>
       </c>
       <c r="M2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2880,7 +2880,7 @@
         <v>161</v>
       </c>
       <c r="M6">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2921,7 +2921,7 @@
         <v>598</v>
       </c>
       <c r="M7">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -3151,7 +3151,7 @@
         <v>24</v>
       </c>
       <c r="M5">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3233,7 +3233,7 @@
         <v>827</v>
       </c>
       <c r="M7">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -3504,7 +3504,7 @@
         <v>39</v>
       </c>
       <c r="M6">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>296</v>
       </c>
       <c r="M7">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3975,7 +3975,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4139,7 +4139,7 @@
         <v>682</v>
       </c>
       <c r="M7">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
@@ -4552,7 +4552,7 @@
         <v>190</v>
       </c>
       <c r="M2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4757,7 +4757,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4798,7 +4798,7 @@
         <v>1427</v>
       </c>
       <c r="M8">
-        <v>1146</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4921,7 +4921,7 @@
         <v>351</v>
       </c>
       <c r="M11">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4962,7 +4962,7 @@
         <v>51</v>
       </c>
       <c r="M12">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -5003,7 +5003,7 @@
         <v>32</v>
       </c>
       <c r="M13">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -5126,7 +5126,7 @@
         <v>50</v>
       </c>
       <c r="M16">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -5208,7 +5208,7 @@
         <v>149</v>
       </c>
       <c r="M18">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -5249,7 +5249,7 @@
         <v>593</v>
       </c>
       <c r="M19">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5290,7 +5290,7 @@
         <v>541</v>
       </c>
       <c r="M20">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5454,7 +5454,7 @@
         <v>68</v>
       </c>
       <c r="M24">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5659,7 +5659,7 @@
         <v>1207</v>
       </c>
       <c r="M29">
-        <v>904</v>
+        <v>907</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5823,7 +5823,7 @@
         <v>973</v>
       </c>
       <c r="M33">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5946,7 +5946,7 @@
         <v>272</v>
       </c>
       <c r="M36">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5987,7 +5987,7 @@
         <v>827</v>
       </c>
       <c r="M37">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6151,7 +6151,7 @@
         <v>93</v>
       </c>
       <c r="M41">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -6192,7 +6192,7 @@
         <v>682</v>
       </c>
       <c r="M42">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6233,7 +6233,7 @@
         <v>167</v>
       </c>
       <c r="M43">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -6397,7 +6397,7 @@
         <v>151</v>
       </c>
       <c r="M47">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6602,7 +6602,7 @@
         <v>459</v>
       </c>
       <c r="M52">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6643,7 +6643,7 @@
         <v>233</v>
       </c>
       <c r="M53">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6725,7 +6725,7 @@
         <v>227</v>
       </c>
       <c r="M55">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6889,7 +6889,7 @@
         <v>36</v>
       </c>
       <c r="M59">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -7053,7 +7053,7 @@
         <v>390</v>
       </c>
       <c r="M63">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7135,7 +7135,7 @@
         <v>434</v>
       </c>
       <c r="M65">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7217,7 +7217,7 @@
         <v>752</v>
       </c>
       <c r="M67">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7299,7 +7299,7 @@
         <v>47</v>
       </c>
       <c r="M69">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -7381,7 +7381,7 @@
         <v>56</v>
       </c>
       <c r="M71">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -7627,7 +7627,7 @@
         <v>143</v>
       </c>
       <c r="M77">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -7709,7 +7709,7 @@
         <v>598</v>
       </c>
       <c r="M79">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7873,7 +7873,7 @@
         <v>479</v>
       </c>
       <c r="M83">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7914,7 +7914,7 @@
         <v>208</v>
       </c>
       <c r="M84">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7955,7 +7955,7 @@
         <v>1080</v>
       </c>
       <c r="M85">
-        <v>860</v>
+        <v>865</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7996,7 +7996,7 @@
         <v>134</v>
       </c>
       <c r="M86">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -8037,7 +8037,7 @@
         <v>59</v>
       </c>
       <c r="M87">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -8078,7 +8078,7 @@
         <v>223</v>
       </c>
       <c r="M88">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -8160,7 +8160,7 @@
         <v>230</v>
       </c>
       <c r="M90">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -8201,7 +8201,7 @@
         <v>296</v>
       </c>
       <c r="M91">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -8365,7 +8365,7 @@
         <v>302</v>
       </c>
       <c r="M95">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8447,7 +8447,7 @@
         <v>173</v>
       </c>
       <c r="M97">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8529,7 +8529,7 @@
         <v>373</v>
       </c>
       <c r="M99">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8611,7 +8611,7 @@
         <v>21929</v>
       </c>
       <c r="M101">
-        <v>16669</v>
+        <v>16742</v>
       </c>
     </row>
   </sheetData>
@@ -8984,7 +8984,7 @@
         <v>62</v>
       </c>
       <c r="M6">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9025,7 +9025,7 @@
         <v>227</v>
       </c>
       <c r="M7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -9132,7 +9132,7 @@
         <v>213</v>
       </c>
       <c r="M2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9337,7 +9337,7 @@
         <v>752</v>
       </c>
       <c r="M7">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -9485,7 +9485,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9608,7 +9608,7 @@
         <v>123</v>
       </c>
       <c r="M6">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9649,7 +9649,7 @@
         <v>541</v>
       </c>
       <c r="M7">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -9797,7 +9797,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9961,7 +9961,7 @@
         <v>479</v>
       </c>
       <c r="M7">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -10232,7 +10232,7 @@
         <v>90</v>
       </c>
       <c r="M6">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10273,7 +10273,7 @@
         <v>351</v>
       </c>
       <c r="M7">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -10380,7 +10380,7 @@
         <v>45</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10585,7 +10585,7 @@
         <v>173</v>
       </c>
       <c r="M7">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -10733,7 +10733,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10897,7 +10897,7 @@
         <v>434</v>
       </c>
       <c r="M7">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -12277,7 +12277,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -12367,7 +12367,7 @@
         <v>32</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -13398,7 +13398,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13562,7 +13562,7 @@
         <v>233</v>
       </c>
       <c r="M7">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -13669,7 +13669,7 @@
         <v>77</v>
       </c>
       <c r="M2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13874,7 +13874,7 @@
         <v>230</v>
       </c>
       <c r="M7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -13981,7 +13981,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14022,7 +14022,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14063,7 +14063,7 @@
         <v>104</v>
       </c>
       <c r="M4">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14145,7 +14145,7 @@
         <v>340</v>
       </c>
       <c r="M6">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14186,7 +14186,7 @@
         <v>1427</v>
       </c>
       <c r="M7">
-        <v>1146</v>
+        <v>1156</v>
       </c>
     </row>
   </sheetData>
@@ -14334,7 +14334,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14486,7 +14486,7 @@
         <v>167</v>
       </c>
       <c r="M7">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -15540,7 +15540,7 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15704,7 +15704,7 @@
         <v>302</v>
       </c>
       <c r="M7">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -16449,7 +16449,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16613,7 +16613,7 @@
         <v>690</v>
       </c>
       <c r="M7">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -17505,7 +17505,7 @@
         <v>164</v>
       </c>
       <c r="M6">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17546,7 +17546,7 @@
         <v>593</v>
       </c>
       <c r="M7">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -17694,7 +17694,7 @@
         <v>150</v>
       </c>
       <c r="M3">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17776,7 +17776,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17858,7 +17858,7 @@
         <v>373</v>
       </c>
       <c r="M7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -17965,7 +17965,7 @@
         <v>50</v>
       </c>
       <c r="M2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18170,7 +18170,7 @@
         <v>143</v>
       </c>
       <c r="M7">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -18615,7 +18615,7 @@
         <v>341</v>
       </c>
       <c r="M3">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18779,7 +18779,7 @@
         <v>973</v>
       </c>
       <c r="M7">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
   </sheetData>
@@ -19515,7 +19515,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19655,7 +19655,7 @@
         <v>51</v>
       </c>
       <c r="M7">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -21108,7 +21108,7 @@
         <v>30</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21149,7 +21149,7 @@
         <v>50</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -21338,7 +21338,7 @@
         <v>16</v>
       </c>
       <c r="M4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -21461,7 +21461,7 @@
         <v>149</v>
       </c>
       <c r="M7">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -21711,7 +21711,7 @@
         <v>17</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21752,7 +21752,7 @@
         <v>134</v>
       </c>
       <c r="M7">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -21941,7 +21941,7 @@
         <v>13</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -22064,7 +22064,7 @@
         <v>223</v>
       </c>
       <c r="M7">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -23765,7 +23765,7 @@
         <v>18</v>
       </c>
       <c r="M4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -23888,7 +23888,7 @@
         <v>190</v>
       </c>
       <c r="M7">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -24613,7 +24613,7 @@
         <v>70</v>
       </c>
       <c r="M2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24777,7 +24777,7 @@
         <v>58</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24818,7 +24818,7 @@
         <v>208</v>
       </c>
       <c r="M7">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -25231,7 +25231,7 @@
         <v>92</v>
       </c>
       <c r="M2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25272,7 +25272,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25433,7 +25433,7 @@
         <v>272</v>
       </c>
       <c r="M7">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -26437,7 +26437,7 @@
         <v>56</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26636,7 +26636,7 @@
         <v>151</v>
       </c>
       <c r="M7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -26895,7 +26895,7 @@
         <v>28</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26936,7 +26936,7 @@
         <v>93</v>
       </c>
       <c r="M7">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -27428,7 +27428,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -27539,7 +27539,7 @@
         <v>59</v>
       </c>
       <c r="M7">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -27922,7 +27922,7 @@
         <v>59</v>
       </c>
       <c r="M2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28086,7 +28086,7 @@
         <v>59</v>
       </c>
       <c r="M6">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -28578,7 +28578,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28742,7 +28742,7 @@
         <v>1080</v>
       </c>
       <c r="M7">
-        <v>860</v>
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -29193,7 +29193,7 @@
         <v>12</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29339,7 +29339,7 @@
         <v>47</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -29446,7 +29446,7 @@
         <v>12</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -29487,7 +29487,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29636,7 +29636,7 @@
         <v>36</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -31486,7 +31486,7 @@
         <v>26</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31676,7 +31676,7 @@
         <v>68</v>
       </c>
       <c r="M7">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -31824,7 +31824,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -31906,7 +31906,7 @@
         <v>13</v>
       </c>
       <c r="M5">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -31947,7 +31947,7 @@
         <v>127</v>
       </c>
       <c r="M6">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -31988,7 +31988,7 @@
         <v>459</v>
       </c>
       <c r="M7">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-full-year.xlsx
+++ b/output/violent-crime-full-year.xlsx
@@ -901,7 +901,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5193</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>7129</v>
       </c>
       <c r="M3">
-        <v>5843</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>1961</v>
       </c>
       <c r="M4">
-        <v>1601</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>5816</v>
       </c>
       <c r="M6">
-        <v>3804</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>21930</v>
       </c>
       <c r="M7">
-        <v>16791</v>
+        <v>16840</v>
       </c>
     </row>
   </sheetData>
@@ -2445,7 +2445,7 @@
         <v>466</v>
       </c>
       <c r="M3">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2609,7 +2609,7 @@
         <v>1207</v>
       </c>
       <c r="M7">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
   </sheetData>
@@ -2798,7 +2798,7 @@
         <v>39</v>
       </c>
       <c r="M4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2921,7 +2921,7 @@
         <v>598</v>
       </c>
       <c r="M7">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -3069,7 +3069,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3233,7 +3233,7 @@
         <v>827</v>
       </c>
       <c r="M7">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -3934,7 +3934,7 @@
         <v>187</v>
       </c>
       <c r="M2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3975,7 +3975,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4098,7 +4098,7 @@
         <v>190</v>
       </c>
       <c r="M6">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4139,7 +4139,7 @@
         <v>682</v>
       </c>
       <c r="M7">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -4798,7 +4798,7 @@
         <v>1427</v>
       </c>
       <c r="M8">
-        <v>1164</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4921,7 +4921,7 @@
         <v>351</v>
       </c>
       <c r="M11">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5085,7 +5085,7 @@
         <v>187</v>
       </c>
       <c r="M15">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -5167,7 +5167,7 @@
         <v>37</v>
       </c>
       <c r="M17">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -5249,7 +5249,7 @@
         <v>593</v>
       </c>
       <c r="M19">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5454,7 +5454,7 @@
         <v>68</v>
       </c>
       <c r="M24">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5495,7 +5495,7 @@
         <v>128</v>
       </c>
       <c r="M25">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5659,7 +5659,7 @@
         <v>1207</v>
       </c>
       <c r="M29">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5823,7 +5823,7 @@
         <v>973</v>
       </c>
       <c r="M33">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5946,7 +5946,7 @@
         <v>272</v>
       </c>
       <c r="M36">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5987,7 +5987,7 @@
         <v>827</v>
       </c>
       <c r="M37">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6192,7 +6192,7 @@
         <v>682</v>
       </c>
       <c r="M42">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6233,7 +6233,7 @@
         <v>167</v>
       </c>
       <c r="M43">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -6479,7 +6479,7 @@
         <v>112</v>
       </c>
       <c r="M49">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6561,7 +6561,7 @@
         <v>267</v>
       </c>
       <c r="M51">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6602,7 +6602,7 @@
         <v>459</v>
       </c>
       <c r="M52">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6684,7 +6684,7 @@
         <v>450</v>
       </c>
       <c r="M54">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6807,7 +6807,7 @@
         <v>75</v>
       </c>
       <c r="M57">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -7053,7 +7053,7 @@
         <v>390</v>
       </c>
       <c r="M63">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7135,7 +7135,7 @@
         <v>434</v>
       </c>
       <c r="M65">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7586,7 +7586,7 @@
         <v>348</v>
       </c>
       <c r="M76">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7627,7 +7627,7 @@
         <v>143</v>
       </c>
       <c r="M77">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -7709,7 +7709,7 @@
         <v>598</v>
       </c>
       <c r="M79">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7750,7 +7750,7 @@
         <v>69</v>
       </c>
       <c r="M80">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -7873,7 +7873,7 @@
         <v>479</v>
       </c>
       <c r="M83">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7914,7 +7914,7 @@
         <v>208</v>
       </c>
       <c r="M84">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7955,7 +7955,7 @@
         <v>1080</v>
       </c>
       <c r="M85">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -8119,7 +8119,7 @@
         <v>289</v>
       </c>
       <c r="M89">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -8160,7 +8160,7 @@
         <v>230</v>
       </c>
       <c r="M90">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -8447,7 +8447,7 @@
         <v>173</v>
       </c>
       <c r="M97">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8529,7 +8529,7 @@
         <v>373</v>
       </c>
       <c r="M99">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8611,7 +8611,7 @@
         <v>21930</v>
       </c>
       <c r="M101">
-        <v>16791</v>
+        <v>16840</v>
       </c>
     </row>
   </sheetData>
@@ -9756,7 +9756,7 @@
         <v>151</v>
       </c>
       <c r="M2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9961,7 +9961,7 @@
         <v>479</v>
       </c>
       <c r="M7">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -10068,7 +10068,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10273,7 +10273,7 @@
         <v>351</v>
       </c>
       <c r="M7">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -10380,7 +10380,7 @@
         <v>45</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10585,7 +10585,7 @@
         <v>173</v>
       </c>
       <c r="M7">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -10692,7 +10692,7 @@
         <v>165</v>
       </c>
       <c r="M2">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10897,7 +10897,7 @@
         <v>434</v>
       </c>
       <c r="M7">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -12515,7 +12515,7 @@
         <v>67</v>
       </c>
       <c r="M3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12556,7 +12556,7 @@
         <v>44</v>
       </c>
       <c r="M4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -12679,7 +12679,7 @@
         <v>348</v>
       </c>
       <c r="M7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -13751,7 +13751,7 @@
         <v>19</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13874,7 +13874,7 @@
         <v>230</v>
       </c>
       <c r="M7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -13981,7 +13981,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14022,7 +14022,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14145,7 +14145,7 @@
         <v>340</v>
       </c>
       <c r="M6">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14186,7 +14186,7 @@
         <v>1427</v>
       </c>
       <c r="M7">
-        <v>1164</v>
+        <v>1168</v>
       </c>
     </row>
   </sheetData>
@@ -14445,7 +14445,7 @@
         <v>49</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14486,7 +14486,7 @@
         <v>167</v>
       </c>
       <c r="M7">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -14928,7 +14928,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15092,7 +15092,7 @@
         <v>187</v>
       </c>
       <c r="M7">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -16761,7 +16761,7 @@
         <v>115</v>
       </c>
       <c r="M3">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16802,7 +16802,7 @@
         <v>38</v>
       </c>
       <c r="M4">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -16881,7 +16881,7 @@
         <v>207</v>
       </c>
       <c r="M6">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16922,7 +16922,7 @@
         <v>450</v>
       </c>
       <c r="M7">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -17070,7 +17070,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17193,7 +17193,7 @@
         <v>19</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17234,7 +17234,7 @@
         <v>128</v>
       </c>
       <c r="M7">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -17341,7 +17341,7 @@
         <v>211</v>
       </c>
       <c r="M2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17505,7 +17505,7 @@
         <v>164</v>
       </c>
       <c r="M6">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17546,7 +17546,7 @@
         <v>593</v>
       </c>
       <c r="M7">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -17735,7 +17735,7 @@
         <v>25</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -17858,7 +17858,7 @@
         <v>373</v>
       </c>
       <c r="M7">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -17965,7 +17965,7 @@
         <v>50</v>
       </c>
       <c r="M2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18170,7 +18170,7 @@
         <v>143</v>
       </c>
       <c r="M7">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18467,7 +18467,7 @@
         <v>112</v>
       </c>
       <c r="M7">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -18656,7 +18656,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18738,7 +18738,7 @@
         <v>271</v>
       </c>
       <c r="M6">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18779,7 +18779,7 @@
         <v>973</v>
       </c>
       <c r="M7">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -19803,7 +19803,7 @@
         <v>79</v>
       </c>
       <c r="M3">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19967,7 +19967,7 @@
         <v>267</v>
       </c>
       <c r="M7">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -24613,7 +24613,7 @@
         <v>70</v>
       </c>
       <c r="M2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24818,7 +24818,7 @@
         <v>208</v>
       </c>
       <c r="M7">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -25083,7 +25083,7 @@
         <v>19</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25124,7 +25124,7 @@
         <v>75</v>
       </c>
       <c r="M7">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -25231,7 +25231,7 @@
         <v>92</v>
       </c>
       <c r="M2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25272,7 +25272,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25433,7 +25433,7 @@
         <v>272</v>
       </c>
       <c r="M7">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -25852,7 +25852,7 @@
         <v>75</v>
       </c>
       <c r="M2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25934,7 +25934,7 @@
         <v>44</v>
       </c>
       <c r="M4">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -26054,7 +26054,7 @@
         <v>289</v>
       </c>
       <c r="M7">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -28537,7 +28537,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28742,7 +28742,7 @@
         <v>1080</v>
       </c>
       <c r="M7">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
   </sheetData>
@@ -31486,7 +31486,7 @@
         <v>26</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31676,7 +31676,7 @@
         <v>68</v>
       </c>
       <c r="M7">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -31824,7 +31824,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -31988,7 +31988,7 @@
         <v>459</v>
       </c>
       <c r="M7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -32505,7 +32505,7 @@
         <v>35</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -32546,7 +32546,7 @@
         <v>69</v>
       </c>
       <c r="M7">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -32694,7 +32694,7 @@
         <v>14</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -32837,7 +32837,7 @@
         <v>37</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
